--- a/research/traditional_assets/database/data/kenya/kenya_food_processing.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_food_processing.xlsx
@@ -1531,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1668,22 +1668,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1341218584402656</v>
+        <v>0.1337509928649448</v>
       </c>
       <c r="C2">
-        <v>36.91224033275024</v>
+        <v>36.70201505789415</v>
       </c>
       <c r="D2">
-        <v>33.43224033275025</v>
+        <v>33.57321505789415</v>
       </c>
       <c r="E2">
-        <v>-8.720000000000001</v>
+        <v>-8.3688</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3512</v>
       </c>
       <c r="G2">
         <v>3.48</v>
@@ -1704,28 +1704,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01766536</v>
       </c>
       <c r="N2">
-        <v>3.414444444444444</v>
+        <v>3.396779084444444</v>
       </c>
       <c r="O2">
-        <v>1.024333333333333</v>
+        <v>1.019033725333333</v>
       </c>
       <c r="P2">
-        <v>2.390111111111111</v>
+        <v>2.377745359111111</v>
       </c>
       <c r="Q2">
-        <v>4.520111111111111</v>
+        <v>4.507745359111111</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1341218584402656</v>
+        <v>0.1347463564292372</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6201733606657254</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>193.2847360282748</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1750,22 +1750,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1337509928649448</v>
+        <v>0.133380127289624</v>
       </c>
       <c r="C3">
-        <v>36.70201505789415</v>
+        <v>36.49298372221498</v>
       </c>
       <c r="D3">
-        <v>33.57321505789415</v>
+        <v>33.71538372221498</v>
       </c>
       <c r="E3">
-        <v>-8.3688</v>
+        <v>-8.017600000000002</v>
       </c>
       <c r="F3">
-        <v>0.3512</v>
+        <v>0.7023999999999999</v>
       </c>
       <c r="G3">
         <v>3.48</v>
@@ -1786,28 +1786,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M3">
-        <v>0.01766536</v>
+        <v>0.03533072</v>
       </c>
       <c r="N3">
-        <v>3.396779084444444</v>
+        <v>3.379113724444444</v>
       </c>
       <c r="O3">
-        <v>1.019033725333333</v>
+        <v>1.013734117333333</v>
       </c>
       <c r="P3">
-        <v>2.377745359111111</v>
+        <v>2.365379607111111</v>
       </c>
       <c r="Q3">
-        <v>4.507745359111111</v>
+        <v>4.495379607111111</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1347463564292372</v>
+        <v>0.1353835992751265</v>
       </c>
       <c r="T3">
-        <v>0.6201733606657254</v>
+        <v>0.6246164998021756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>193.2847360282748</v>
+        <v>96.64236801413739</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.133380127289624</v>
+        <v>0.1330092617143032</v>
       </c>
       <c r="C4">
-        <v>36.49298372221498</v>
+        <v>36.28516155772816</v>
       </c>
       <c r="D4">
-        <v>33.71538372221498</v>
+        <v>33.85876155772817</v>
       </c>
       <c r="E4">
-        <v>-8.017600000000002</v>
+        <v>-7.666400000000001</v>
       </c>
       <c r="F4">
-        <v>0.7023999999999999</v>
+        <v>1.0536</v>
       </c>
       <c r="G4">
         <v>3.48</v>
@@ -1868,28 +1868,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M4">
-        <v>0.03533072</v>
+        <v>0.05299607999999999</v>
       </c>
       <c r="N4">
-        <v>3.379113724444444</v>
+        <v>3.361448364444444</v>
       </c>
       <c r="O4">
-        <v>1.013734117333333</v>
+        <v>1.008434509333333</v>
       </c>
       <c r="P4">
-        <v>2.365379607111111</v>
+        <v>2.353013855111111</v>
       </c>
       <c r="Q4">
-        <v>4.495379607111111</v>
+        <v>4.483013855111111</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1353835992751265</v>
+        <v>0.1360339811487662</v>
       </c>
       <c r="T4">
-        <v>0.6246164998021756</v>
+        <v>0.6291512500548413</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.64236801413739</v>
+        <v>64.42824534275826</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1914,22 +1914,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1330092617143032</v>
+        <v>0.1326383961389824</v>
       </c>
       <c r="C5">
-        <v>36.28516155772816</v>
+        <v>36.07856405665802</v>
       </c>
       <c r="D5">
-        <v>33.85876155772817</v>
+        <v>34.00336405665802</v>
       </c>
       <c r="E5">
-        <v>-7.666400000000001</v>
+        <v>-7.315200000000001</v>
       </c>
       <c r="F5">
-        <v>1.0536</v>
+        <v>1.4048</v>
       </c>
       <c r="G5">
         <v>3.48</v>
@@ -1950,28 +1950,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M5">
-        <v>0.05299607999999999</v>
+        <v>0.07066143999999999</v>
       </c>
       <c r="N5">
-        <v>3.361448364444444</v>
+        <v>3.343783004444444</v>
       </c>
       <c r="O5">
-        <v>1.008434509333333</v>
+        <v>1.003134901333333</v>
       </c>
       <c r="P5">
-        <v>2.353013855111111</v>
+        <v>2.340648103111111</v>
       </c>
       <c r="Q5">
-        <v>4.483013855111111</v>
+        <v>4.470648103111111</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1360339811487662</v>
+        <v>0.1366979126447733</v>
       </c>
       <c r="T5">
-        <v>0.6291512500548413</v>
+        <v>0.6337804742711042</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.42824534275826</v>
+        <v>48.3211840070687</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1996,22 +1996,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1326383961389824</v>
+        <v>0.1322675305636616</v>
       </c>
       <c r="C6">
-        <v>36.07856405665802</v>
+        <v>35.87320697701794</v>
       </c>
       <c r="D6">
-        <v>34.00336405665802</v>
+        <v>34.14920697701795</v>
       </c>
       <c r="E6">
-        <v>-7.315200000000001</v>
+        <v>-6.964</v>
       </c>
       <c r="F6">
-        <v>1.4048</v>
+        <v>1.756</v>
       </c>
       <c r="G6">
         <v>3.48</v>
@@ -2032,28 +2032,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M6">
-        <v>0.07066143999999999</v>
+        <v>0.0883268</v>
       </c>
       <c r="N6">
-        <v>3.343783004444444</v>
+        <v>3.326117644444444</v>
       </c>
       <c r="O6">
-        <v>1.003134901333333</v>
+        <v>0.9978352933333332</v>
       </c>
       <c r="P6">
-        <v>2.340648103111111</v>
+        <v>2.328282351111111</v>
       </c>
       <c r="Q6">
-        <v>4.470648103111111</v>
+        <v>4.45828235111111</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1366979126447733</v>
+        <v>0.1373758216459596</v>
       </c>
       <c r="T6">
-        <v>0.6337804742711042</v>
+        <v>0.6385071558392884</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.3211840070687</v>
+        <v>38.65694720565496</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2078,22 +2078,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1322675305636616</v>
+        <v>0.1318966649883408</v>
       </c>
       <c r="C7">
-        <v>35.87320697701794</v>
+        <v>35.669106348335</v>
       </c>
       <c r="D7">
-        <v>34.14920697701795</v>
+        <v>34.296306348335</v>
       </c>
       <c r="E7">
-        <v>-6.964</v>
+        <v>-6.6128</v>
       </c>
       <c r="F7">
-        <v>1.756</v>
+        <v>2.1072</v>
       </c>
       <c r="G7">
         <v>3.48</v>
@@ -2114,28 +2114,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M7">
-        <v>0.0883268</v>
+        <v>0.10599216</v>
       </c>
       <c r="N7">
-        <v>3.326117644444444</v>
+        <v>3.308452284444444</v>
       </c>
       <c r="O7">
-        <v>0.9978352933333332</v>
+        <v>0.9925356853333331</v>
       </c>
       <c r="P7">
-        <v>2.328282351111111</v>
+        <v>2.315916599111111</v>
       </c>
       <c r="Q7">
-        <v>4.45828235111111</v>
+        <v>4.445916599111111</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1373758216459596</v>
+        <v>0.1380681542429158</v>
       </c>
       <c r="T7">
-        <v>0.6385071558392884</v>
+        <v>0.6433344051004128</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.65694720565496</v>
+        <v>32.21412267137913</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2160,22 +2160,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1318966649883408</v>
+        <v>0.13152579941302</v>
       </c>
       <c r="C8">
-        <v>35.669106348335</v>
+        <v>35.46627847752301</v>
       </c>
       <c r="D8">
-        <v>34.296306348335</v>
+        <v>34.44467847752301</v>
       </c>
       <c r="E8">
-        <v>-6.612800000000001</v>
+        <v>-6.261600000000001</v>
       </c>
       <c r="F8">
-        <v>2.1072</v>
+        <v>2.4584</v>
       </c>
       <c r="G8">
         <v>3.48</v>
@@ -2196,28 +2196,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M8">
-        <v>0.10599216</v>
+        <v>0.12365752</v>
       </c>
       <c r="N8">
-        <v>3.308452284444444</v>
+        <v>3.290786924444444</v>
       </c>
       <c r="O8">
-        <v>0.9925356853333331</v>
+        <v>0.9872360773333331</v>
       </c>
       <c r="P8">
-        <v>2.315916599111111</v>
+        <v>2.303550847111111</v>
       </c>
       <c r="Q8">
-        <v>4.445916599111111</v>
+        <v>4.43355084711111</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1380681542429158</v>
+        <v>0.1387753757129248</v>
       </c>
       <c r="T8">
-        <v>0.6433344051004128</v>
+        <v>0.6482654661736044</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.21412267137913</v>
+        <v>27.6121051468964</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2242,22 +2242,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.13152579941302</v>
+        <v>0.1311549338376992</v>
       </c>
       <c r="C9">
-        <v>35.46627847752301</v>
+        <v>35.26473995490868</v>
       </c>
       <c r="D9">
-        <v>34.44467847752301</v>
+        <v>34.59433995490868</v>
       </c>
       <c r="E9">
-        <v>-6.2616</v>
+        <v>-5.910400000000001</v>
       </c>
       <c r="F9">
-        <v>2.4584</v>
+        <v>2.8096</v>
       </c>
       <c r="G9">
         <v>3.48</v>
@@ -2278,28 +2278,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M9">
-        <v>0.12365752</v>
+        <v>0.14132288</v>
       </c>
       <c r="N9">
-        <v>3.290786924444444</v>
+        <v>3.273121564444444</v>
       </c>
       <c r="O9">
-        <v>0.9872360773333331</v>
+        <v>0.9819364693333331</v>
       </c>
       <c r="P9">
-        <v>2.303550847111111</v>
+        <v>2.291185095111111</v>
       </c>
       <c r="Q9">
-        <v>4.43355084711111</v>
+        <v>4.421185095111111</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1387753757129248</v>
+        <v>0.1394979715627165</v>
       </c>
       <c r="T9">
-        <v>0.6482654661736044</v>
+        <v>0.653303724226648</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.61210514689639</v>
+        <v>24.16059200353435</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2324,22 +2324,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1311549338376992</v>
+        <v>0.1307840682623784</v>
       </c>
       <c r="C10">
-        <v>35.26473995490868</v>
+        <v>35.06450766041565</v>
       </c>
       <c r="D10">
-        <v>34.59433995490868</v>
+        <v>34.74530766041565</v>
       </c>
       <c r="E10">
-        <v>-5.910400000000001</v>
+        <v>-5.559200000000001</v>
       </c>
       <c r="F10">
-        <v>2.8096</v>
+        <v>3.1608</v>
       </c>
       <c r="G10">
         <v>3.48</v>
@@ -2360,28 +2360,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M10">
-        <v>0.14132288</v>
+        <v>0.15898824</v>
       </c>
       <c r="N10">
-        <v>3.273121564444444</v>
+        <v>3.255456204444444</v>
       </c>
       <c r="O10">
-        <v>0.9819364693333331</v>
+        <v>0.9766368613333332</v>
       </c>
       <c r="P10">
-        <v>2.291185095111111</v>
+        <v>2.278819343111111</v>
       </c>
       <c r="Q10">
-        <v>4.421185095111111</v>
+        <v>4.408819343111111</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1394979715627165</v>
+        <v>0.1402364486399763</v>
       </c>
       <c r="T10">
-        <v>0.653303724226648</v>
+        <v>0.6584527132259121</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.16059200353435</v>
+        <v>21.47608178091942</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2406,22 +2406,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1307840682623784</v>
+        <v>0.1304132026870576</v>
       </c>
       <c r="C11">
-        <v>35.06450766041565</v>
+        <v>34.86559876991114</v>
       </c>
       <c r="D11">
-        <v>34.74530766041565</v>
+        <v>34.89759876991115</v>
       </c>
       <c r="E11">
-        <v>-5.559200000000001</v>
+        <v>-5.208000000000001</v>
       </c>
       <c r="F11">
-        <v>3.1608</v>
+        <v>3.512</v>
       </c>
       <c r="G11">
         <v>3.48</v>
@@ -2442,28 +2442,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M11">
-        <v>0.15898824</v>
+        <v>0.1766536</v>
       </c>
       <c r="N11">
-        <v>3.255456204444444</v>
+        <v>3.237790844444444</v>
       </c>
       <c r="O11">
-        <v>0.9766368613333332</v>
+        <v>0.9713372533333332</v>
       </c>
       <c r="P11">
-        <v>2.278819343111111</v>
+        <v>2.266453591111111</v>
       </c>
       <c r="Q11">
-        <v>4.408819343111111</v>
+        <v>4.396453591111111</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1402364486399763</v>
+        <v>0.1409913363189529</v>
       </c>
       <c r="T11">
-        <v>0.6584527132259121</v>
+        <v>0.6637161242029378</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.47608178091942</v>
+        <v>19.32847360282748</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2488,22 +2488,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1304132026870576</v>
+        <v>0.1300423371117368</v>
       </c>
       <c r="C12">
-        <v>34.86559876991114</v>
+        <v>34.6680307617201</v>
       </c>
       <c r="D12">
-        <v>34.89759876991115</v>
+        <v>35.05123076172011</v>
       </c>
       <c r="E12">
-        <v>-5.208</v>
+        <v>-4.856800000000002</v>
       </c>
       <c r="F12">
-        <v>3.512</v>
+        <v>3.8632</v>
       </c>
       <c r="G12">
         <v>3.48</v>
@@ -2524,28 +2524,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M12">
-        <v>0.1766536</v>
+        <v>0.19431896</v>
       </c>
       <c r="N12">
-        <v>3.237790844444444</v>
+        <v>3.220125484444444</v>
       </c>
       <c r="O12">
-        <v>0.9713372533333332</v>
+        <v>0.9660376453333331</v>
       </c>
       <c r="P12">
-        <v>2.266453591111111</v>
+        <v>2.254087839111111</v>
       </c>
       <c r="Q12">
-        <v>4.396453591111111</v>
+        <v>4.384087839111111</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1409913363189529</v>
+        <v>0.1417631877659964</v>
       </c>
       <c r="T12">
-        <v>0.6637161242029378</v>
+        <v>0.6690978140783236</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.32847360282748</v>
+        <v>17.57133963893407</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2570,22 +2570,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1300423371117368</v>
+        <v>0.129671471536416</v>
       </c>
       <c r="C13">
-        <v>34.6680307617201</v>
+        <v>34.47182142331238</v>
       </c>
       <c r="D13">
-        <v>35.05123076172011</v>
+        <v>35.20622142331238</v>
       </c>
       <c r="E13">
-        <v>-4.856800000000002</v>
+        <v>-4.505600000000001</v>
       </c>
       <c r="F13">
-        <v>3.8632</v>
+        <v>4.214399999999999</v>
       </c>
       <c r="G13">
         <v>3.48</v>
@@ -2606,28 +2606,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M13">
-        <v>0.19431896</v>
+        <v>0.21198432</v>
       </c>
       <c r="N13">
-        <v>3.220125484444444</v>
+        <v>3.202460124444444</v>
       </c>
       <c r="O13">
-        <v>0.9660376453333331</v>
+        <v>0.9607380373333332</v>
       </c>
       <c r="P13">
-        <v>2.254087839111111</v>
+        <v>2.241722087111111</v>
       </c>
       <c r="Q13">
-        <v>4.384087839111111</v>
+        <v>4.371722087111111</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1417631877659964</v>
+        <v>0.1425525812913818</v>
       </c>
       <c r="T13">
-        <v>0.6690978140783236</v>
+        <v>0.6746018150872409</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.57133963893407</v>
+        <v>16.10706133568956</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2652,22 +2652,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.129671471536416</v>
+        <v>0.1293006059610952</v>
       </c>
       <c r="C14">
-        <v>34.47182142331238</v>
+        <v>34.27698885816802</v>
       </c>
       <c r="D14">
-        <v>35.20622142331238</v>
+        <v>35.36258885816803</v>
       </c>
       <c r="E14">
-        <v>-4.505600000000001</v>
+        <v>-4.154400000000001</v>
       </c>
       <c r="F14">
-        <v>4.214399999999999</v>
+        <v>4.5656</v>
       </c>
       <c r="G14">
         <v>3.48</v>
@@ -2688,28 +2688,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M14">
-        <v>0.21198432</v>
+        <v>0.22964968</v>
       </c>
       <c r="N14">
-        <v>3.202460124444444</v>
+        <v>3.184794764444444</v>
       </c>
       <c r="O14">
-        <v>0.9607380373333332</v>
+        <v>0.9554384293333331</v>
       </c>
       <c r="P14">
-        <v>2.241722087111111</v>
+        <v>2.229356335111111</v>
       </c>
       <c r="Q14">
-        <v>4.371722087111111</v>
+        <v>4.35935633511111</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1425525812913818</v>
+        <v>0.1433601217943623</v>
       </c>
       <c r="T14">
-        <v>0.6746018150872409</v>
+        <v>0.6802323448549839</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.10706133568956</v>
+        <v>14.8680566175596</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2734,22 +2734,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1293006059610952</v>
+        <v>0.1289297403857744</v>
       </c>
       <c r="C15">
-        <v>34.27698885816802</v>
+        <v>34.08355149282629</v>
       </c>
       <c r="D15">
-        <v>35.36258885816803</v>
+        <v>35.52035149282629</v>
       </c>
       <c r="E15">
-        <v>-4.154400000000001</v>
+        <v>-3.8032</v>
       </c>
       <c r="F15">
-        <v>4.5656</v>
+        <v>4.9168</v>
       </c>
       <c r="G15">
         <v>3.48</v>
@@ -2770,28 +2770,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M15">
-        <v>0.22964968</v>
+        <v>0.24731504</v>
       </c>
       <c r="N15">
-        <v>3.184794764444444</v>
+        <v>3.167129404444444</v>
       </c>
       <c r="O15">
-        <v>0.9554384293333331</v>
+        <v>0.9501388213333331</v>
       </c>
       <c r="P15">
-        <v>2.229356335111111</v>
+        <v>2.216990583111111</v>
       </c>
       <c r="Q15">
-        <v>4.35935633511111</v>
+        <v>4.346990583111111</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1433601217943623</v>
+        <v>0.14418644230904</v>
       </c>
       <c r="T15">
-        <v>0.6802323448549839</v>
+        <v>0.685993817175465</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.8680566175596</v>
+        <v>13.8060525734482</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2816,22 +2816,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1289297403857744</v>
+        <v>0.1285588748104536</v>
       </c>
       <c r="C16">
-        <v>34.08355149282629</v>
+        <v>33.89152808412427</v>
       </c>
       <c r="D16">
-        <v>35.52035149282629</v>
+        <v>35.67952808412428</v>
       </c>
       <c r="E16">
-        <v>-3.8032</v>
+        <v>-3.452</v>
       </c>
       <c r="F16">
-        <v>4.9168</v>
+        <v>5.268000000000001</v>
       </c>
       <c r="G16">
         <v>3.48</v>
@@ -2852,28 +2852,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M16">
-        <v>0.24731504</v>
+        <v>0.2649804</v>
       </c>
       <c r="N16">
-        <v>3.167129404444444</v>
+        <v>3.149464044444444</v>
       </c>
       <c r="O16">
-        <v>0.9501388213333331</v>
+        <v>0.9448392133333331</v>
       </c>
       <c r="P16">
-        <v>2.216990583111111</v>
+        <v>2.204624831111111</v>
       </c>
       <c r="Q16">
-        <v>4.346990583111111</v>
+        <v>4.33462483111111</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.14418644230904</v>
+        <v>0.1450322056593572</v>
       </c>
       <c r="T16">
-        <v>0.685993817175465</v>
+        <v>0.6918908535505458</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.8060525734482</v>
+        <v>12.88564906855165</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2898,22 +2898,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1285588748104536</v>
+        <v>0.1283560092351329</v>
       </c>
       <c r="C17">
-        <v>33.89152808412427</v>
+        <v>33.62800368834763</v>
       </c>
       <c r="D17">
-        <v>35.67952808412428</v>
+        <v>35.76720368834763</v>
       </c>
       <c r="E17">
-        <v>-3.452000000000001</v>
+        <v>-3.100800000000001</v>
       </c>
       <c r="F17">
-        <v>5.268</v>
+        <v>5.619199999999999</v>
       </c>
       <c r="G17">
         <v>3.48</v>
@@ -2934,45 +2934,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M17">
-        <v>0.2649803999999999</v>
+        <v>0.29107456</v>
       </c>
       <c r="N17">
-        <v>3.149464044444444</v>
+        <v>3.123369884444444</v>
       </c>
       <c r="O17">
-        <v>0.9448392133333332</v>
+        <v>0.9370109653333332</v>
       </c>
       <c r="P17">
-        <v>2.204624831111111</v>
+        <v>2.186358919111111</v>
       </c>
       <c r="Q17">
-        <v>4.334624831111111</v>
+        <v>4.316358919111112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1450322056593572</v>
+        <v>0.145898106232301</v>
       </c>
       <c r="T17">
-        <v>0.6918908535505458</v>
+        <v>0.6979282955536047</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.88564906855165</v>
+        <v>11.73048048048048</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2980,22 +2980,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1283560092351329</v>
+        <v>0.127995643659812</v>
       </c>
       <c r="C18">
-        <v>33.62800368834763</v>
+        <v>33.43361575722215</v>
       </c>
       <c r="D18">
-        <v>35.76720368834763</v>
+        <v>35.92401575722215</v>
       </c>
       <c r="E18">
-        <v>-3.100800000000001</v>
+        <v>-2.749600000000001</v>
       </c>
       <c r="F18">
-        <v>5.619199999999999</v>
+        <v>5.9704</v>
       </c>
       <c r="G18">
         <v>3.48</v>
@@ -3016,28 +3016,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M18">
-        <v>0.29107456</v>
+        <v>0.30926672</v>
       </c>
       <c r="N18">
-        <v>3.123369884444444</v>
+        <v>3.105177724444444</v>
       </c>
       <c r="O18">
-        <v>0.9370109653333332</v>
+        <v>0.9315533173333331</v>
       </c>
       <c r="P18">
-        <v>2.186358919111111</v>
+        <v>2.173624407111111</v>
       </c>
       <c r="Q18">
-        <v>4.316358919111112</v>
+        <v>4.303624407111111</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.145898106232301</v>
+        <v>0.1467848718792916</v>
       </c>
       <c r="T18">
-        <v>0.6979282955536047</v>
+        <v>0.7041112180868578</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.73048048048048</v>
+        <v>11.0404522169228</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.127995643659812</v>
+        <v>0.1276352780844912</v>
       </c>
       <c r="C19">
-        <v>33.43361575722215</v>
+        <v>33.24060888504191</v>
       </c>
       <c r="D19">
-        <v>35.92401575722215</v>
+        <v>36.08220888504191</v>
       </c>
       <c r="E19">
-        <v>-2.749600000000001</v>
+        <v>-2.398400000000001</v>
       </c>
       <c r="F19">
-        <v>5.9704</v>
+        <v>6.3216</v>
       </c>
       <c r="G19">
         <v>3.48</v>
@@ -3098,28 +3098,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M19">
-        <v>0.30926672</v>
+        <v>0.32745888</v>
       </c>
       <c r="N19">
-        <v>3.105177724444444</v>
+        <v>3.086985564444444</v>
       </c>
       <c r="O19">
-        <v>0.9315533173333331</v>
+        <v>0.9260956693333331</v>
       </c>
       <c r="P19">
-        <v>2.173624407111111</v>
+        <v>2.160889895111111</v>
       </c>
       <c r="Q19">
-        <v>4.303624407111111</v>
+        <v>4.290889895111111</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1467848718792916</v>
+        <v>0.1476932659566966</v>
       </c>
       <c r="T19">
-        <v>0.7041112180868578</v>
+        <v>0.7104449436087267</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.0404522169228</v>
+        <v>10.42709376042709</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3144,22 +3144,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1276352780844912</v>
+        <v>0.1272749125091704</v>
       </c>
       <c r="C20">
-        <v>33.2406088850419</v>
+        <v>33.04900139718162</v>
       </c>
       <c r="D20">
-        <v>36.0822088850419</v>
+        <v>36.24180139718163</v>
       </c>
       <c r="E20">
-        <v>-2.398400000000001</v>
+        <v>-2.047200000000001</v>
       </c>
       <c r="F20">
-        <v>6.321599999999999</v>
+        <v>6.6728</v>
       </c>
       <c r="G20">
         <v>3.48</v>
@@ -3180,28 +3180,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M20">
-        <v>0.32745888</v>
+        <v>0.34565104</v>
       </c>
       <c r="N20">
-        <v>3.086985564444444</v>
+        <v>3.068793404444444</v>
       </c>
       <c r="O20">
-        <v>0.9260956693333331</v>
+        <v>0.9206380213333332</v>
       </c>
       <c r="P20">
-        <v>2.160889895111111</v>
+        <v>2.148155383111111</v>
       </c>
       <c r="Q20">
-        <v>4.290889895111111</v>
+        <v>4.278155383111111</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1476932659566966</v>
+        <v>0.1486240895174944</v>
       </c>
       <c r="T20">
-        <v>0.7104449436087267</v>
+        <v>0.7169350574150862</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.42709376042709</v>
+        <v>9.878299351983562</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3226,22 +3226,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1272749125091704</v>
+        <v>0.1271525469338497</v>
       </c>
       <c r="C21">
-        <v>33.04900139718162</v>
+        <v>32.75231412045547</v>
       </c>
       <c r="D21">
-        <v>36.24180139718163</v>
+        <v>36.29631412045547</v>
       </c>
       <c r="E21">
-        <v>-2.047200000000001</v>
+        <v>-1.696000000000001</v>
       </c>
       <c r="F21">
-        <v>6.6728</v>
+        <v>7.024</v>
       </c>
       <c r="G21">
         <v>3.48</v>
@@ -3262,45 +3262,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M21">
-        <v>0.34565104</v>
+        <v>0.375784</v>
       </c>
       <c r="N21">
-        <v>3.068793404444444</v>
+        <v>3.038660444444444</v>
       </c>
       <c r="O21">
-        <v>0.9206380213333332</v>
+        <v>0.9115981333333332</v>
       </c>
       <c r="P21">
-        <v>2.148155383111111</v>
+        <v>2.127062311111111</v>
       </c>
       <c r="Q21">
-        <v>4.278155383111111</v>
+        <v>4.257062311111111</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1486240895174944</v>
+        <v>0.1495781836673121</v>
       </c>
       <c r="T21">
-        <v>0.7169350574150862</v>
+        <v>0.7235874240666049</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.878299351983562</v>
+        <v>9.086188992731048</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3308,22 +3308,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1271525469338497</v>
+        <v>0.1268040813585289</v>
       </c>
       <c r="C22">
-        <v>32.75231412045547</v>
+        <v>32.55725459843988</v>
       </c>
       <c r="D22">
-        <v>36.29631412045547</v>
+        <v>36.45245459843988</v>
       </c>
       <c r="E22">
-        <v>-1.696000000000001</v>
+        <v>-1.3448</v>
       </c>
       <c r="F22">
-        <v>7.024</v>
+        <v>7.3752</v>
       </c>
       <c r="G22">
         <v>3.48</v>
@@ -3344,28 +3344,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M22">
-        <v>0.375784</v>
+        <v>0.3945732</v>
       </c>
       <c r="N22">
-        <v>3.038660444444444</v>
+        <v>3.019871244444444</v>
       </c>
       <c r="O22">
-        <v>0.9115981333333332</v>
+        <v>0.9059613733333332</v>
       </c>
       <c r="P22">
-        <v>2.127062311111111</v>
+        <v>2.113909871111111</v>
       </c>
       <c r="Q22">
-        <v>4.257062311111111</v>
+        <v>4.243909871111111</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1495781836673121</v>
+        <v>0.1505564320994036</v>
       </c>
       <c r="T22">
-        <v>0.7235874240666049</v>
+        <v>0.7304082050637316</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.086188992731048</v>
+        <v>8.653513326410522</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3390,22 +3390,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1268040813585289</v>
+        <v>0.1264556157832081</v>
       </c>
       <c r="C23">
-        <v>32.55725459843989</v>
+        <v>32.36354425914303</v>
       </c>
       <c r="D23">
-        <v>36.45245459843989</v>
+        <v>36.60994425914303</v>
       </c>
       <c r="E23">
-        <v>-1.344800000000001</v>
+        <v>-0.9936000000000016</v>
       </c>
       <c r="F23">
-        <v>7.3752</v>
+        <v>7.726399999999999</v>
       </c>
       <c r="G23">
         <v>3.48</v>
@@ -3426,28 +3426,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M23">
-        <v>0.3945732</v>
+        <v>0.4133624</v>
       </c>
       <c r="N23">
-        <v>3.019871244444444</v>
+        <v>3.001082044444444</v>
       </c>
       <c r="O23">
-        <v>0.9059613733333332</v>
+        <v>0.9003246133333331</v>
       </c>
       <c r="P23">
-        <v>2.113909871111111</v>
+        <v>2.100757431111111</v>
       </c>
       <c r="Q23">
-        <v>4.243909871111111</v>
+        <v>4.230757431111112</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1505564320994036</v>
+        <v>0.1515597638246257</v>
       </c>
       <c r="T23">
-        <v>0.7304082050637315</v>
+        <v>0.7374038778812972</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.653513326410522</v>
+        <v>8.260171811573681</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3472,22 +3472,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1264556157832081</v>
+        <v>0.1261071502078873</v>
       </c>
       <c r="C24">
-        <v>32.36354425914303</v>
+        <v>32.17120066552404</v>
       </c>
       <c r="D24">
-        <v>36.60994425914303</v>
+        <v>36.76880066552405</v>
       </c>
       <c r="E24">
-        <v>-0.9936000000000016</v>
+        <v>-0.6424000000000003</v>
       </c>
       <c r="F24">
-        <v>7.726399999999999</v>
+        <v>8.0776</v>
       </c>
       <c r="G24">
         <v>3.48</v>
@@ -3508,28 +3508,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M24">
-        <v>0.4133624</v>
+        <v>0.4321516</v>
       </c>
       <c r="N24">
-        <v>3.001082044444444</v>
+        <v>2.982292844444444</v>
       </c>
       <c r="O24">
-        <v>0.9003246133333331</v>
+        <v>0.8946878533333331</v>
       </c>
       <c r="P24">
-        <v>2.100757431111111</v>
+        <v>2.087604991111111</v>
       </c>
       <c r="Q24">
-        <v>4.230757431111112</v>
+        <v>4.217604991111111</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1515597638246257</v>
+        <v>0.1525891561141393</v>
       </c>
       <c r="T24">
-        <v>0.7374038778812972</v>
+        <v>0.7445812564863322</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.260171811573681</v>
+        <v>7.90103390672265</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3554,22 +3554,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1261071502078873</v>
+        <v>0.1258930846325665</v>
       </c>
       <c r="C25">
-        <v>32.17120066552404</v>
+        <v>31.91827300082527</v>
       </c>
       <c r="D25">
-        <v>36.76880066552405</v>
+        <v>36.86707300082528</v>
       </c>
       <c r="E25">
-        <v>-0.6424000000000003</v>
+        <v>-0.2911999999999999</v>
       </c>
       <c r="F25">
-        <v>8.0776</v>
+        <v>8.428800000000001</v>
       </c>
       <c r="G25">
         <v>3.48</v>
@@ -3590,45 +3590,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M25">
-        <v>0.4321516</v>
+        <v>0.4576838400000001</v>
       </c>
       <c r="N25">
-        <v>2.982292844444444</v>
+        <v>2.956760604444444</v>
       </c>
       <c r="O25">
-        <v>0.8946878533333331</v>
+        <v>0.8870281813333332</v>
       </c>
       <c r="P25">
-        <v>2.087604991111111</v>
+        <v>2.069732423111111</v>
       </c>
       <c r="Q25">
-        <v>4.217604991111111</v>
+        <v>4.199732423111112</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1525891561141393</v>
+        <v>0.1536456376744296</v>
       </c>
       <c r="T25">
-        <v>0.7445812564863322</v>
+        <v>0.7519475134757103</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.90103390672265</v>
+        <v>7.460268740195073</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3636,22 +3636,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1258930846325665</v>
+        <v>0.1255502190572457</v>
       </c>
       <c r="C26">
-        <v>31.91827300082528</v>
+        <v>31.72557350833796</v>
       </c>
       <c r="D26">
-        <v>36.86707300082528</v>
+        <v>37.02557350833796</v>
       </c>
       <c r="E26">
-        <v>-0.2912000000000017</v>
+        <v>0.05999999999999872</v>
       </c>
       <c r="F26">
-        <v>8.428799999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G26">
         <v>3.48</v>
@@ -3672,28 +3672,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M26">
-        <v>0.45768384</v>
+        <v>0.476754</v>
       </c>
       <c r="N26">
-        <v>2.956760604444444</v>
+        <v>2.937690444444444</v>
       </c>
       <c r="O26">
-        <v>0.8870281813333332</v>
+        <v>0.8813071333333331</v>
       </c>
       <c r="P26">
-        <v>2.069732423111111</v>
+        <v>2.056383311111111</v>
       </c>
       <c r="Q26">
-        <v>4.199732423111112</v>
+        <v>4.186383311111111</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1536456376744296</v>
+        <v>0.1547302920763276</v>
       </c>
       <c r="T26">
-        <v>0.7519475134757103</v>
+        <v>0.7595102039848052</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.460268740195075</v>
+        <v>7.161857990587271</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3718,22 +3718,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1255502190572457</v>
+        <v>0.1252073534819249</v>
       </c>
       <c r="C27">
-        <v>31.72557350833796</v>
+        <v>31.53424276484716</v>
       </c>
       <c r="D27">
-        <v>37.02557350833796</v>
+        <v>37.18544276484716</v>
       </c>
       <c r="E27">
-        <v>0.05999999999999872</v>
+        <v>0.4111999999999991</v>
       </c>
       <c r="F27">
-        <v>8.779999999999999</v>
+        <v>9.1312</v>
       </c>
       <c r="G27">
         <v>3.48</v>
@@ -3754,28 +3754,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M27">
-        <v>0.476754</v>
+        <v>0.49582416</v>
       </c>
       <c r="N27">
-        <v>2.937690444444444</v>
+        <v>2.918620284444444</v>
       </c>
       <c r="O27">
-        <v>0.8813071333333331</v>
+        <v>0.8755860853333332</v>
       </c>
       <c r="P27">
-        <v>2.056383311111111</v>
+        <v>2.043034199111111</v>
       </c>
       <c r="Q27">
-        <v>4.186383311111111</v>
+        <v>4.173034199111111</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1547302920763276</v>
+        <v>0.1558442614620607</v>
       </c>
       <c r="T27">
-        <v>0.7595102039848052</v>
+        <v>0.7672772915346863</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.161857990587271</v>
+        <v>6.886401914026222</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3800,22 +3800,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1252073534819249</v>
+        <v>0.1248644879066041</v>
       </c>
       <c r="C28">
-        <v>31.53424276484716</v>
+        <v>31.34429857721881</v>
       </c>
       <c r="D28">
-        <v>37.18544276484716</v>
+        <v>37.34669857721881</v>
       </c>
       <c r="E28">
-        <v>0.4111999999999991</v>
+        <v>0.7623999999999995</v>
       </c>
       <c r="F28">
-        <v>9.1312</v>
+        <v>9.4824</v>
       </c>
       <c r="G28">
         <v>3.48</v>
@@ -3836,28 +3836,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M28">
-        <v>0.49582416</v>
+        <v>0.51489432</v>
       </c>
       <c r="N28">
-        <v>2.918620284444444</v>
+        <v>2.899550124444444</v>
       </c>
       <c r="O28">
-        <v>0.8755860853333332</v>
+        <v>0.8698650373333331</v>
       </c>
       <c r="P28">
-        <v>2.043034199111111</v>
+        <v>2.029685087111111</v>
       </c>
       <c r="Q28">
-        <v>4.173034199111111</v>
+        <v>4.159685087111111</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1558442614620607</v>
+        <v>0.1569887505569919</v>
       </c>
       <c r="T28">
-        <v>0.7672772915346863</v>
+        <v>0.7752571760037423</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.886401914026222</v>
+        <v>6.63134999128451</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3882,22 +3882,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1248644879066041</v>
+        <v>0.1245216223312833</v>
       </c>
       <c r="C29">
-        <v>31.34429857721881</v>
+        <v>31.15575906254423</v>
       </c>
       <c r="D29">
-        <v>37.34669857721881</v>
+        <v>37.50935906254423</v>
       </c>
       <c r="E29">
-        <v>0.7623999999999995</v>
+        <v>1.1136</v>
       </c>
       <c r="F29">
-        <v>9.4824</v>
+        <v>9.833600000000001</v>
       </c>
       <c r="G29">
         <v>3.48</v>
@@ -3918,28 +3918,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M29">
-        <v>0.51489432</v>
+        <v>0.5339644800000001</v>
       </c>
       <c r="N29">
-        <v>2.899550124444444</v>
+        <v>2.880479964444444</v>
       </c>
       <c r="O29">
-        <v>0.8698650373333331</v>
+        <v>0.864143989333333</v>
       </c>
       <c r="P29">
-        <v>2.029685087111111</v>
+        <v>2.016335975111111</v>
       </c>
       <c r="Q29">
-        <v>4.159685087111111</v>
+        <v>4.146335975111111</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1569887505569919</v>
+        <v>0.1581650310156712</v>
       </c>
       <c r="T29">
-        <v>0.7752571760037423</v>
+        <v>0.7834587239302719</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.63134999128451</v>
+        <v>6.394516063024348</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3964,22 +3964,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1245216223312833</v>
+        <v>0.1241787567559625</v>
       </c>
       <c r="C30">
-        <v>31.15575906254423</v>
+        <v>30.96864265492545</v>
       </c>
       <c r="D30">
-        <v>37.50935906254423</v>
+        <v>37.67344265492546</v>
       </c>
       <c r="E30">
-        <v>1.1136</v>
+        <v>1.4648</v>
       </c>
       <c r="F30">
-        <v>9.833600000000001</v>
+        <v>10.1848</v>
       </c>
       <c r="G30">
         <v>3.48</v>
@@ -4000,28 +4000,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M30">
-        <v>0.5339644800000001</v>
+        <v>0.55303464</v>
       </c>
       <c r="N30">
-        <v>2.880479964444444</v>
+        <v>2.861409804444444</v>
       </c>
       <c r="O30">
-        <v>0.864143989333333</v>
+        <v>0.8584229413333332</v>
       </c>
       <c r="P30">
-        <v>2.016335975111111</v>
+        <v>2.002986863111111</v>
       </c>
       <c r="Q30">
-        <v>4.146335975111111</v>
+        <v>4.132986863111111</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1581650310156712</v>
+        <v>0.1593744461351584</v>
       </c>
       <c r="T30">
-        <v>0.7834587239302719</v>
+        <v>0.7918913013758589</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.394516063024348</v>
+        <v>6.174015509126958</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4046,22 +4046,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1241787567559625</v>
+        <v>0.1240458911806417</v>
       </c>
       <c r="C31">
-        <v>30.96864265492546</v>
+        <v>30.68141411153659</v>
       </c>
       <c r="D31">
-        <v>37.67344265492546</v>
+        <v>37.73741411153659</v>
       </c>
       <c r="E31">
-        <v>1.464799999999999</v>
+        <v>1.815999999999999</v>
       </c>
       <c r="F31">
-        <v>10.1848</v>
+        <v>10.536</v>
       </c>
       <c r="G31">
         <v>3.48</v>
@@ -4082,45 +4082,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M31">
-        <v>0.55303464</v>
+        <v>0.5826408</v>
       </c>
       <c r="N31">
-        <v>2.861409804444444</v>
+        <v>2.831803644444444</v>
       </c>
       <c r="O31">
-        <v>0.8584229413333332</v>
+        <v>0.8495410933333332</v>
       </c>
       <c r="P31">
-        <v>2.002986863111111</v>
+        <v>1.982262551111111</v>
       </c>
       <c r="Q31">
-        <v>4.132986863111111</v>
+        <v>4.112262551111111</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1593744461351584</v>
+        <v>0.1606184159723453</v>
       </c>
       <c r="T31">
-        <v>0.7918913013758589</v>
+        <v>0.8005648096056054</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.174015509126958</v>
+        <v>5.860290670417252</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4128,22 +4128,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1240458911806417</v>
+        <v>0.1237100256053209</v>
       </c>
       <c r="C32">
-        <v>30.68141411153659</v>
+        <v>30.49289790227104</v>
       </c>
       <c r="D32">
-        <v>37.73741411153659</v>
+        <v>37.90009790227104</v>
       </c>
       <c r="E32">
-        <v>1.815999999999999</v>
+        <v>2.167199999999999</v>
       </c>
       <c r="F32">
-        <v>10.536</v>
+        <v>10.8872</v>
       </c>
       <c r="G32">
         <v>3.48</v>
@@ -4164,28 +4164,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M32">
-        <v>0.5826408</v>
+        <v>0.60206216</v>
       </c>
       <c r="N32">
-        <v>2.831803644444444</v>
+        <v>2.812382284444444</v>
       </c>
       <c r="O32">
-        <v>0.8495410933333332</v>
+        <v>0.8437146853333332</v>
       </c>
       <c r="P32">
-        <v>1.982262551111111</v>
+        <v>1.968667599111111</v>
       </c>
       <c r="Q32">
-        <v>4.112262551111111</v>
+        <v>4.098667599111112</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1606184159723453</v>
+        <v>0.1618984429062622</v>
       </c>
       <c r="T32">
-        <v>0.8005648096056054</v>
+        <v>0.8094897238709967</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.860290670417252</v>
+        <v>5.671249035887663</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4210,22 +4210,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1237100256053209</v>
+        <v>0.1233741600300001</v>
       </c>
       <c r="C33">
-        <v>30.49289790227104</v>
+        <v>30.30579040655001</v>
       </c>
       <c r="D33">
-        <v>37.90009790227104</v>
+        <v>38.06419040655001</v>
       </c>
       <c r="E33">
-        <v>2.167199999999999</v>
+        <v>2.518399999999998</v>
       </c>
       <c r="F33">
-        <v>10.8872</v>
+        <v>11.2384</v>
       </c>
       <c r="G33">
         <v>3.48</v>
@@ -4246,28 +4246,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M33">
-        <v>0.60206216</v>
+        <v>0.62148352</v>
       </c>
       <c r="N33">
-        <v>2.812382284444444</v>
+        <v>2.792960924444444</v>
       </c>
       <c r="O33">
-        <v>0.8437146853333332</v>
+        <v>0.8378882773333332</v>
       </c>
       <c r="P33">
-        <v>1.968667599111111</v>
+        <v>1.955072647111111</v>
       </c>
       <c r="Q33">
-        <v>4.098667599111112</v>
+        <v>4.085072647111112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1618984429062622</v>
+        <v>0.1632161176911766</v>
       </c>
       <c r="T33">
-        <v>0.8094897238709967</v>
+        <v>0.8186771356147819</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.671249035887663</v>
+        <v>5.494022503516174</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4292,22 +4292,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1233741600300001</v>
+        <v>0.1230382944546793</v>
       </c>
       <c r="C34">
-        <v>30.30579040655001</v>
+        <v>30.12011000146439</v>
       </c>
       <c r="D34">
-        <v>38.06419040655001</v>
+        <v>38.22971000146439</v>
       </c>
       <c r="E34">
-        <v>2.518399999999998</v>
+        <v>2.869599999999998</v>
       </c>
       <c r="F34">
-        <v>11.2384</v>
+        <v>11.5896</v>
       </c>
       <c r="G34">
         <v>3.48</v>
@@ -4328,28 +4328,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M34">
-        <v>0.62148352</v>
+        <v>0.64090488</v>
       </c>
       <c r="N34">
-        <v>2.792960924444444</v>
+        <v>2.773539564444444</v>
       </c>
       <c r="O34">
-        <v>0.8378882773333332</v>
+        <v>0.8320618693333331</v>
       </c>
       <c r="P34">
-        <v>1.955072647111111</v>
+        <v>1.941477695111111</v>
       </c>
       <c r="Q34">
-        <v>4.085072647111112</v>
+        <v>4.071477695111112</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1632161176911766</v>
+        <v>0.1645731260517602</v>
       </c>
       <c r="T34">
-        <v>0.8186771356147819</v>
+        <v>0.8281387984553967</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.494022503516174</v>
+        <v>5.327536973106593</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4374,22 +4374,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1230382944546793</v>
+        <v>0.1227024288793585</v>
       </c>
       <c r="C35">
-        <v>30.12011000146439</v>
+        <v>29.93587538514729</v>
       </c>
       <c r="D35">
-        <v>38.22971000146439</v>
+        <v>38.39667538514729</v>
       </c>
       <c r="E35">
-        <v>2.869599999999998</v>
+        <v>3.220799999999999</v>
       </c>
       <c r="F35">
-        <v>11.5896</v>
+        <v>11.9408</v>
       </c>
       <c r="G35">
         <v>3.48</v>
@@ -4410,28 +4410,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M35">
-        <v>0.64090488</v>
+        <v>0.66032624</v>
       </c>
       <c r="N35">
-        <v>2.773539564444444</v>
+        <v>2.754118204444444</v>
       </c>
       <c r="O35">
-        <v>0.8320618693333331</v>
+        <v>0.8262354613333333</v>
       </c>
       <c r="P35">
-        <v>1.941477695111111</v>
+        <v>1.927882743111111</v>
       </c>
       <c r="Q35">
-        <v>4.071477695111112</v>
+        <v>4.057882743111112</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1645731260517602</v>
+        <v>0.1659712558778159</v>
       </c>
       <c r="T35">
-        <v>0.8281387984553967</v>
+        <v>0.8378871783517875</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.327536973106593</v>
+        <v>5.170844709191694</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4456,22 +4456,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1227024288793585</v>
+        <v>0.1223665633040377</v>
       </c>
       <c r="C36">
-        <v>29.93587538514729</v>
+        <v>29.75310558381546</v>
       </c>
       <c r="D36">
-        <v>38.39667538514729</v>
+        <v>38.56510558381547</v>
       </c>
       <c r="E36">
-        <v>3.220799999999999</v>
+        <v>3.571999999999999</v>
       </c>
       <c r="F36">
-        <v>11.9408</v>
+        <v>12.292</v>
       </c>
       <c r="G36">
         <v>3.48</v>
@@ -4492,28 +4492,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M36">
-        <v>0.66032624</v>
+        <v>0.6797476</v>
       </c>
       <c r="N36">
-        <v>2.754118204444444</v>
+        <v>2.734696844444444</v>
       </c>
       <c r="O36">
-        <v>0.8262354613333333</v>
+        <v>0.8204090533333331</v>
       </c>
       <c r="P36">
-        <v>1.927882743111111</v>
+        <v>1.914287791111111</v>
       </c>
       <c r="Q36">
-        <v>4.057882743111112</v>
+        <v>4.044287791111111</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1659712558778159</v>
+        <v>0.1674124050831349</v>
       </c>
       <c r="T36">
-        <v>0.8378871783517875</v>
+        <v>0.8479355083988365</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.170844709191694</v>
+        <v>5.023106288929073</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4538,22 +4538,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1223665633040377</v>
+        <v>0.1220306977287169</v>
       </c>
       <c r="C37">
-        <v>29.75310558381546</v>
+        <v>29.57181995899684</v>
       </c>
       <c r="D37">
-        <v>38.56510558381547</v>
+        <v>38.73501995899684</v>
       </c>
       <c r="E37">
-        <v>3.571999999999999</v>
+        <v>3.9232</v>
       </c>
       <c r="F37">
-        <v>12.292</v>
+        <v>12.6432</v>
       </c>
       <c r="G37">
         <v>3.48</v>
@@ -4574,28 +4574,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M37">
-        <v>0.6797476</v>
+        <v>0.6991689600000001</v>
       </c>
       <c r="N37">
-        <v>2.734696844444444</v>
+        <v>2.715275484444444</v>
       </c>
       <c r="O37">
-        <v>0.8204090533333331</v>
+        <v>0.8145826453333331</v>
       </c>
       <c r="P37">
-        <v>1.914287791111111</v>
+        <v>1.900692839111111</v>
       </c>
       <c r="Q37">
-        <v>4.044287791111111</v>
+        <v>4.030692839111111</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1674124050831349</v>
+        <v>0.1688985902011202</v>
       </c>
       <c r="T37">
-        <v>0.8479355083988365</v>
+        <v>0.8582978487598558</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.023106288929073</v>
+        <v>4.883575558681043</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4620,22 +4620,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1220306977287169</v>
+        <v>0.1216948321533961</v>
       </c>
       <c r="C38">
-        <v>29.57181995899683</v>
+        <v>29.39203821494998</v>
       </c>
       <c r="D38">
-        <v>38.73501995899684</v>
+        <v>38.90643821494998</v>
       </c>
       <c r="E38">
-        <v>3.923199999999998</v>
+        <v>4.274399999999998</v>
       </c>
       <c r="F38">
-        <v>12.6432</v>
+        <v>12.9944</v>
       </c>
       <c r="G38">
         <v>3.48</v>
@@ -4656,28 +4656,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M38">
-        <v>0.69916896</v>
+        <v>0.71859032</v>
       </c>
       <c r="N38">
-        <v>2.715275484444444</v>
+        <v>2.695854124444444</v>
       </c>
       <c r="O38">
-        <v>0.8145826453333331</v>
+        <v>0.8087562373333331</v>
       </c>
       <c r="P38">
-        <v>1.900692839111111</v>
+        <v>1.887097887111111</v>
       </c>
       <c r="Q38">
-        <v>4.030692839111111</v>
+        <v>4.017097887111111</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1688985902011202</v>
+        <v>0.1704319557990414</v>
       </c>
       <c r="T38">
-        <v>0.8582978487598558</v>
+        <v>0.8689891523069391</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.883575558681043</v>
+        <v>4.751587030068042</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4702,22 +4702,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1216948321533961</v>
+        <v>0.1213589665780753</v>
       </c>
       <c r="C39">
-        <v>29.39203821494998</v>
+        <v>29.21378040628136</v>
       </c>
       <c r="D39">
-        <v>38.90643821494998</v>
+        <v>39.07938040628136</v>
       </c>
       <c r="E39">
-        <v>4.274399999999998</v>
+        <v>4.625599999999999</v>
       </c>
       <c r="F39">
-        <v>12.9944</v>
+        <v>13.3456</v>
       </c>
       <c r="G39">
         <v>3.48</v>
@@ -4738,28 +4738,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M39">
-        <v>0.71859032</v>
+        <v>0.7380116799999999</v>
       </c>
       <c r="N39">
-        <v>2.695854124444444</v>
+        <v>2.676432764444444</v>
       </c>
       <c r="O39">
-        <v>0.8087562373333331</v>
+        <v>0.8029298293333331</v>
       </c>
       <c r="P39">
-        <v>1.887097887111111</v>
+        <v>1.873502935111111</v>
       </c>
       <c r="Q39">
-        <v>4.017097887111111</v>
+        <v>4.003502935111111</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1704319557990414</v>
+        <v>0.1720147848033473</v>
       </c>
       <c r="T39">
-        <v>0.8689891523069391</v>
+        <v>0.8800253366136059</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.751587030068042</v>
+        <v>4.626545266118884</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4784,22 +4784,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1213589665780753</v>
+        <v>0.1210231010027545</v>
       </c>
       <c r="C40">
-        <v>29.21378040628136</v>
+        <v>29.03706694576681</v>
       </c>
       <c r="D40">
-        <v>39.07938040628136</v>
+        <v>39.25386694576682</v>
       </c>
       <c r="E40">
-        <v>4.625599999999999</v>
+        <v>4.976799999999999</v>
       </c>
       <c r="F40">
-        <v>13.3456</v>
+        <v>13.6968</v>
       </c>
       <c r="G40">
         <v>3.48</v>
@@ -4820,28 +4820,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M40">
-        <v>0.7380116799999999</v>
+        <v>0.75743304</v>
       </c>
       <c r="N40">
-        <v>2.676432764444444</v>
+        <v>2.657011404444444</v>
       </c>
       <c r="O40">
-        <v>0.8029298293333331</v>
+        <v>0.7971034213333331</v>
       </c>
       <c r="P40">
-        <v>1.873502935111111</v>
+        <v>1.859907983111111</v>
       </c>
       <c r="Q40">
-        <v>4.003502935111111</v>
+        <v>3.989907983111111</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1720147848033473</v>
+        <v>0.1736495098405812</v>
       </c>
       <c r="T40">
-        <v>0.8800253366136059</v>
+        <v>0.891423363028688</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.626545266118884</v>
+        <v>4.507915900320963</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4866,22 +4866,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1210231010027545</v>
+        <v>0.1213872354274337</v>
       </c>
       <c r="C41">
-        <v>29.03706694576681</v>
+        <v>28.49676511956689</v>
       </c>
       <c r="D41">
-        <v>39.25386694576682</v>
+        <v>39.0647651195669</v>
       </c>
       <c r="E41">
-        <v>4.976799999999999</v>
+        <v>5.327999999999999</v>
       </c>
       <c r="F41">
-        <v>13.6968</v>
+        <v>14.048</v>
       </c>
       <c r="G41">
         <v>3.48</v>
@@ -4902,45 +4902,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M41">
-        <v>0.75743304</v>
+        <v>0.8119744000000001</v>
       </c>
       <c r="N41">
-        <v>2.657011404444444</v>
+        <v>2.602470044444444</v>
       </c>
       <c r="O41">
-        <v>0.7971034213333331</v>
+        <v>0.7807410133333331</v>
       </c>
       <c r="P41">
-        <v>1.859907983111111</v>
+        <v>1.821729031111111</v>
       </c>
       <c r="Q41">
-        <v>3.989907983111111</v>
+        <v>3.951729031111111</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1736495098405812</v>
+        <v>0.1753387257123896</v>
       </c>
       <c r="T41">
-        <v>0.891423363028688</v>
+        <v>0.9032013236576062</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.507915900320963</v>
+        <v>4.205113417916185</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4948,22 +4948,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1213872354274337</v>
+        <v>0.1210688698521129</v>
       </c>
       <c r="C42">
-        <v>28.49676511956689</v>
+        <v>28.31079779074289</v>
       </c>
       <c r="D42">
-        <v>39.0647651195669</v>
+        <v>39.22999779074289</v>
       </c>
       <c r="E42">
-        <v>5.327999999999999</v>
+        <v>5.6792</v>
       </c>
       <c r="F42">
-        <v>14.048</v>
+        <v>14.3992</v>
       </c>
       <c r="G42">
         <v>3.48</v>
@@ -4984,28 +4984,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M42">
-        <v>0.8119744000000001</v>
+        <v>0.8322737600000001</v>
       </c>
       <c r="N42">
-        <v>2.602470044444444</v>
+        <v>2.582170684444444</v>
       </c>
       <c r="O42">
-        <v>0.7807410133333331</v>
+        <v>0.7746512053333331</v>
       </c>
       <c r="P42">
-        <v>1.821729031111111</v>
+        <v>1.807519479111111</v>
       </c>
       <c r="Q42">
-        <v>3.951729031111111</v>
+        <v>3.937519479111111</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1753387257123896</v>
+        <v>0.1770852031391744</v>
       </c>
       <c r="T42">
-        <v>0.9032013236576062</v>
+        <v>0.9153785371891994</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.205113417916185</v>
+        <v>4.102549676015791</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5030,22 +5030,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1210688698521129</v>
+        <v>0.1207505042767921</v>
       </c>
       <c r="C43">
-        <v>28.31079779074289</v>
+        <v>28.12623417213882</v>
       </c>
       <c r="D43">
-        <v>39.22999779074289</v>
+        <v>39.39663417213882</v>
       </c>
       <c r="E43">
-        <v>5.6792</v>
+        <v>6.0304</v>
       </c>
       <c r="F43">
-        <v>14.3992</v>
+        <v>14.7504</v>
       </c>
       <c r="G43">
         <v>3.48</v>
@@ -5066,28 +5066,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M43">
-        <v>0.8322737600000001</v>
+        <v>0.8525731200000001</v>
       </c>
       <c r="N43">
-        <v>2.582170684444444</v>
+        <v>2.561871324444444</v>
       </c>
       <c r="O43">
-        <v>0.7746512053333331</v>
+        <v>0.7685613973333331</v>
       </c>
       <c r="P43">
-        <v>1.807519479111111</v>
+        <v>1.793309927111111</v>
       </c>
       <c r="Q43">
-        <v>3.937519479111111</v>
+        <v>3.923309927111111</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1770852031391744</v>
+        <v>0.1788919039255037</v>
       </c>
       <c r="T43">
-        <v>0.9153785371891994</v>
+        <v>0.9279756546356752</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.102549676015791</v>
+        <v>4.004869921824938</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5112,22 +5112,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1207505042767921</v>
+        <v>0.1214856387014713</v>
       </c>
       <c r="C44">
-        <v>28.1262341721388</v>
+        <v>27.39237476021698</v>
       </c>
       <c r="D44">
-        <v>39.3966341721388</v>
+        <v>39.01397476021698</v>
       </c>
       <c r="E44">
-        <v>6.030399999999998</v>
+        <v>6.381599999999999</v>
       </c>
       <c r="F44">
-        <v>14.7504</v>
+        <v>15.1016</v>
       </c>
       <c r="G44">
         <v>3.48</v>
@@ -5148,45 +5148,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M44">
-        <v>0.85257312</v>
+        <v>0.92572808</v>
       </c>
       <c r="N44">
-        <v>2.561871324444444</v>
+        <v>2.488716364444444</v>
       </c>
       <c r="O44">
-        <v>0.7685613973333331</v>
+        <v>0.7466149093333332</v>
       </c>
       <c r="P44">
-        <v>1.793309927111111</v>
+        <v>1.742101455111111</v>
       </c>
       <c r="Q44">
-        <v>3.923309927111111</v>
+        <v>3.872101455111111</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1788919039255037</v>
+        <v>0.1807619977218795</v>
       </c>
       <c r="T44">
-        <v>0.9279756546356751</v>
+        <v>0.9410147762030799</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.004869921824938</v>
+        <v>3.68838811116591</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5194,22 +5194,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1214856387014713</v>
+        <v>0.1211917731261505</v>
       </c>
       <c r="C45">
-        <v>27.39237476021698</v>
+        <v>27.1932452536285</v>
       </c>
       <c r="D45">
-        <v>39.01397476021698</v>
+        <v>39.1660452536285</v>
       </c>
       <c r="E45">
-        <v>6.381599999999999</v>
+        <v>6.732799999999997</v>
       </c>
       <c r="F45">
-        <v>15.1016</v>
+        <v>15.4528</v>
       </c>
       <c r="G45">
         <v>3.48</v>
@@ -5230,28 +5230,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M45">
-        <v>0.92572808</v>
+        <v>0.9472566399999999</v>
       </c>
       <c r="N45">
-        <v>2.488716364444444</v>
+        <v>2.467187804444444</v>
       </c>
       <c r="O45">
-        <v>0.7466149093333332</v>
+        <v>0.7401563413333332</v>
       </c>
       <c r="P45">
-        <v>1.742101455111111</v>
+        <v>1.727031463111111</v>
       </c>
       <c r="Q45">
-        <v>3.872101455111111</v>
+        <v>3.857031463111111</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1807619977218795</v>
+        <v>0.1826988805824117</v>
       </c>
       <c r="T45">
-        <v>0.9410147762030799</v>
+        <v>0.9545195806836063</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.68838811116591</v>
+        <v>3.604561108639412</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5276,22 +5276,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1211917731261505</v>
+        <v>0.1208979075508298</v>
       </c>
       <c r="C46">
-        <v>27.1932452536285</v>
+        <v>26.99530588094632</v>
       </c>
       <c r="D46">
-        <v>39.1660452536285</v>
+        <v>39.31930588094632</v>
       </c>
       <c r="E46">
-        <v>6.732799999999997</v>
+        <v>7.083999999999998</v>
       </c>
       <c r="F46">
-        <v>15.4528</v>
+        <v>15.804</v>
       </c>
       <c r="G46">
         <v>3.48</v>
@@ -5312,28 +5312,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M46">
-        <v>0.9472566399999999</v>
+        <v>0.9687851999999999</v>
       </c>
       <c r="N46">
-        <v>2.467187804444444</v>
+        <v>2.445659244444444</v>
       </c>
       <c r="O46">
-        <v>0.7401563413333332</v>
+        <v>0.7336977733333333</v>
       </c>
       <c r="P46">
-        <v>1.727031463111111</v>
+        <v>1.711961471111111</v>
       </c>
       <c r="Q46">
-        <v>3.857031463111111</v>
+        <v>3.841961471111111</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1826988805824117</v>
+        <v>0.1847061955469632</v>
       </c>
       <c r="T46">
-        <v>0.9545195806836063</v>
+        <v>0.9685154689634248</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.604561108639412</v>
+        <v>3.524459750669648</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5358,22 +5358,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1208979075508298</v>
+        <v>0.1215056419755089</v>
       </c>
       <c r="C47">
-        <v>26.99530588094632</v>
+        <v>26.32846631809747</v>
       </c>
       <c r="D47">
-        <v>39.31930588094632</v>
+        <v>39.00366631809747</v>
       </c>
       <c r="E47">
-        <v>7.083999999999998</v>
+        <v>7.4352</v>
       </c>
       <c r="F47">
-        <v>15.804</v>
+        <v>16.1552</v>
       </c>
       <c r="G47">
         <v>3.48</v>
@@ -5394,45 +5394,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M47">
-        <v>0.9687851999999999</v>
+        <v>1.03554832</v>
       </c>
       <c r="N47">
-        <v>2.445659244444444</v>
+        <v>2.378896124444444</v>
       </c>
       <c r="O47">
-        <v>0.7336977733333333</v>
+        <v>0.7136688373333331</v>
       </c>
       <c r="P47">
-        <v>1.711961471111111</v>
+        <v>1.665227287111111</v>
       </c>
       <c r="Q47">
-        <v>3.841961471111111</v>
+        <v>3.795227287111111</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1847061955469632</v>
+        <v>0.1867878555102017</v>
       </c>
       <c r="T47">
-        <v>0.9685154689634248</v>
+        <v>0.9830297234758287</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.524459750669648</v>
+        <v>3.297233338608906</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5440,22 +5440,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1215056419755089</v>
+        <v>0.1212313764001881</v>
       </c>
       <c r="C48">
-        <v>26.32846631809747</v>
+        <v>26.11908214451963</v>
       </c>
       <c r="D48">
-        <v>39.00366631809747</v>
+        <v>39.14548214451963</v>
       </c>
       <c r="E48">
-        <v>7.4352</v>
+        <v>7.786399999999999</v>
       </c>
       <c r="F48">
-        <v>16.1552</v>
+        <v>16.5064</v>
       </c>
       <c r="G48">
         <v>3.48</v>
@@ -5476,28 +5476,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M48">
-        <v>1.03554832</v>
+        <v>1.05806024</v>
       </c>
       <c r="N48">
-        <v>2.378896124444444</v>
+        <v>2.356384204444444</v>
       </c>
       <c r="O48">
-        <v>0.7136688373333331</v>
+        <v>0.7069152613333332</v>
       </c>
       <c r="P48">
-        <v>1.665227287111111</v>
+        <v>1.649468943111111</v>
       </c>
       <c r="Q48">
-        <v>3.795227287111111</v>
+        <v>3.779468943111111</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1867878555102017</v>
+        <v>0.1889480686796003</v>
       </c>
       <c r="T48">
-        <v>0.9830297234758287</v>
+        <v>0.9980916857056822</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.297233338608906</v>
+        <v>3.22707943778744</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5522,22 +5522,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1212313764001881</v>
+        <v>0.1209571108248673</v>
       </c>
       <c r="C49">
-        <v>26.11908214451963</v>
+        <v>25.91073300804729</v>
       </c>
       <c r="D49">
-        <v>39.14548214451963</v>
+        <v>39.2883330080473</v>
       </c>
       <c r="E49">
-        <v>7.786399999999999</v>
+        <v>8.137600000000001</v>
       </c>
       <c r="F49">
-        <v>16.5064</v>
+        <v>16.8576</v>
       </c>
       <c r="G49">
         <v>3.48</v>
@@ -5558,28 +5558,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M49">
-        <v>1.05806024</v>
+        <v>1.08057216</v>
       </c>
       <c r="N49">
-        <v>2.356384204444444</v>
+        <v>2.333872284444444</v>
       </c>
       <c r="O49">
-        <v>0.7069152613333332</v>
+        <v>0.700161685333333</v>
       </c>
       <c r="P49">
-        <v>1.649468943111111</v>
+        <v>1.63371059911111</v>
       </c>
       <c r="Q49">
-        <v>3.779468943111111</v>
+        <v>3.763710599111111</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1889480686796003</v>
+        <v>0.1911913669708987</v>
       </c>
       <c r="T49">
-        <v>0.9980916857056822</v>
+        <v>1.013732954175145</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.22707943778744</v>
+        <v>3.159848616166868</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5604,22 +5604,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1209571108248673</v>
+        <v>0.1206828452495465</v>
       </c>
       <c r="C50">
-        <v>25.91073300804729</v>
+        <v>25.70343028144734</v>
       </c>
       <c r="D50">
-        <v>39.2883330080473</v>
+        <v>39.43223028144734</v>
       </c>
       <c r="E50">
-        <v>8.137599999999997</v>
+        <v>8.488799999999999</v>
       </c>
       <c r="F50">
-        <v>16.8576</v>
+        <v>17.2088</v>
       </c>
       <c r="G50">
         <v>3.48</v>
@@ -5640,28 +5640,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M50">
-        <v>1.08057216</v>
+        <v>1.10308408</v>
       </c>
       <c r="N50">
-        <v>2.333872284444444</v>
+        <v>2.311360364444444</v>
       </c>
       <c r="O50">
-        <v>0.7001616853333331</v>
+        <v>0.6934081093333332</v>
       </c>
       <c r="P50">
-        <v>1.633710599111111</v>
+        <v>1.617952255111111</v>
       </c>
       <c r="Q50">
-        <v>3.763710599111111</v>
+        <v>3.747952255111111</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1911913669708987</v>
+        <v>0.1935226377442089</v>
       </c>
       <c r="T50">
-        <v>1.013732954175145</v>
+        <v>1.029987605721842</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.159848616166868</v>
+        <v>3.095361909714483</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5686,22 +5686,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1206828452495465</v>
+        <v>0.1204085796742257</v>
       </c>
       <c r="C51">
-        <v>25.70343028144734</v>
+        <v>25.4971855047145</v>
       </c>
       <c r="D51">
-        <v>39.43223028144734</v>
+        <v>39.57718550471451</v>
       </c>
       <c r="E51">
-        <v>8.488799999999999</v>
+        <v>8.839999999999998</v>
       </c>
       <c r="F51">
-        <v>17.2088</v>
+        <v>17.56</v>
       </c>
       <c r="G51">
         <v>3.48</v>
@@ -5722,28 +5722,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M51">
-        <v>1.10308408</v>
+        <v>1.125596</v>
       </c>
       <c r="N51">
-        <v>2.311360364444444</v>
+        <v>2.288848444444444</v>
       </c>
       <c r="O51">
-        <v>0.6934081093333332</v>
+        <v>0.686654533333333</v>
       </c>
       <c r="P51">
-        <v>1.617952255111111</v>
+        <v>1.602193911111111</v>
       </c>
       <c r="Q51">
-        <v>3.747952255111111</v>
+        <v>3.732193911111111</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1935226377442089</v>
+        <v>0.1959471593484515</v>
       </c>
       <c r="T51">
-        <v>1.029987605721842</v>
+        <v>1.046892443330407</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.095361909714483</v>
+        <v>3.033454671520194</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5768,22 +5768,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1204085796742257</v>
+        <v>0.122918914098905</v>
       </c>
       <c r="C52">
-        <v>25.4971855047145</v>
+        <v>23.85768972973795</v>
       </c>
       <c r="D52">
-        <v>39.57718550471451</v>
+        <v>38.28888972973795</v>
       </c>
       <c r="E52">
-        <v>8.839999999999998</v>
+        <v>9.191199999999997</v>
       </c>
       <c r="F52">
-        <v>17.56</v>
+        <v>17.9112</v>
       </c>
       <c r="G52">
         <v>3.48</v>
@@ -5804,45 +5804,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M52">
-        <v>1.125596</v>
+        <v>1.28781528</v>
       </c>
       <c r="N52">
-        <v>2.288848444444444</v>
+        <v>2.126629164444444</v>
       </c>
       <c r="O52">
-        <v>0.686654533333333</v>
+        <v>0.6379887493333333</v>
       </c>
       <c r="P52">
-        <v>1.602193911111111</v>
+        <v>1.488640415111111</v>
       </c>
       <c r="Q52">
-        <v>3.732193911111111</v>
+        <v>3.618640415111111</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1959471593484515</v>
+        <v>0.1984706410181734</v>
       </c>
       <c r="T52">
-        <v>1.046892443330407</v>
+        <v>1.06448727431075</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.033454671520194</v>
+        <v>2.65134642946964</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5850,22 +5850,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.122918914098905</v>
+        <v>0.1226992485235842</v>
       </c>
       <c r="C53">
-        <v>23.85768972973795</v>
+        <v>23.61586337320467</v>
       </c>
       <c r="D53">
-        <v>38.28888972973795</v>
+        <v>38.39826337320467</v>
       </c>
       <c r="E53">
-        <v>9.191199999999997</v>
+        <v>9.542399999999999</v>
       </c>
       <c r="F53">
-        <v>17.9112</v>
+        <v>18.2624</v>
       </c>
       <c r="G53">
         <v>3.48</v>
@@ -5886,28 +5886,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M53">
-        <v>1.28781528</v>
+        <v>1.31306656</v>
       </c>
       <c r="N53">
-        <v>2.126629164444444</v>
+        <v>2.101377884444444</v>
       </c>
       <c r="O53">
-        <v>0.6379887493333333</v>
+        <v>0.6304133653333333</v>
       </c>
       <c r="P53">
-        <v>1.488640415111111</v>
+        <v>1.470964519111111</v>
       </c>
       <c r="Q53">
-        <v>3.618640415111111</v>
+        <v>3.600964519111111</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1984706410181734</v>
+        <v>0.201099267757467</v>
       </c>
       <c r="T53">
-        <v>1.06448727431075</v>
+        <v>1.082815223248607</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.65134642946964</v>
+        <v>2.600358998133685</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5932,22 +5932,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1226992485235842</v>
+        <v>0.1224795829482634</v>
       </c>
       <c r="C54">
-        <v>23.61586337320467</v>
+        <v>23.37466366651463</v>
       </c>
       <c r="D54">
-        <v>38.39826337320467</v>
+        <v>38.50826366651463</v>
       </c>
       <c r="E54">
-        <v>9.542399999999999</v>
+        <v>9.893599999999998</v>
       </c>
       <c r="F54">
-        <v>18.2624</v>
+        <v>18.6136</v>
       </c>
       <c r="G54">
         <v>3.48</v>
@@ -5968,28 +5968,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M54">
-        <v>1.31306656</v>
+        <v>1.33831784</v>
       </c>
       <c r="N54">
-        <v>2.101377884444444</v>
+        <v>2.076126604444444</v>
       </c>
       <c r="O54">
-        <v>0.6304133653333333</v>
+        <v>0.6228379813333332</v>
       </c>
       <c r="P54">
-        <v>1.470964519111111</v>
+        <v>1.453288623111111</v>
       </c>
       <c r="Q54">
-        <v>3.600964519111111</v>
+        <v>3.583288623111111</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.201099267757467</v>
+        <v>0.2038397509537518</v>
       </c>
       <c r="T54">
-        <v>1.082815223248607</v>
+        <v>1.101923084907224</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.600358998133685</v>
+        <v>2.551295620810408</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6014,22 +6014,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1224795829482634</v>
+        <v>0.1222599173729426</v>
       </c>
       <c r="C55">
-        <v>23.37466366651463</v>
+        <v>23.13409601067019</v>
       </c>
       <c r="D55">
-        <v>38.50826366651463</v>
+        <v>38.6188960106702</v>
       </c>
       <c r="E55">
-        <v>9.893599999999998</v>
+        <v>10.2448</v>
       </c>
       <c r="F55">
-        <v>18.6136</v>
+        <v>18.9648</v>
       </c>
       <c r="G55">
         <v>3.48</v>
@@ -6050,28 +6050,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M55">
-        <v>1.33831784</v>
+        <v>1.36356912</v>
       </c>
       <c r="N55">
-        <v>2.076126604444444</v>
+        <v>2.050875324444444</v>
       </c>
       <c r="O55">
-        <v>0.6228379813333332</v>
+        <v>0.6152625973333331</v>
       </c>
       <c r="P55">
-        <v>1.453288623111111</v>
+        <v>1.435612727111111</v>
       </c>
       <c r="Q55">
-        <v>3.583288623111111</v>
+        <v>3.565612727111111</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2038397509537518</v>
+        <v>0.2066993855933534</v>
       </c>
       <c r="T55">
-        <v>1.101923084907224</v>
+        <v>1.121861723159695</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.551295620810408</v>
+        <v>2.504049405610215</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6096,22 +6096,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1222599173729426</v>
+        <v>0.1235417517976218</v>
       </c>
       <c r="C56">
-        <v>23.13409601067019</v>
+        <v>22.14613353484574</v>
       </c>
       <c r="D56">
-        <v>38.6188960106702</v>
+        <v>37.98213353484574</v>
       </c>
       <c r="E56">
-        <v>10.2448</v>
+        <v>10.596</v>
       </c>
       <c r="F56">
-        <v>18.9648</v>
+        <v>19.316</v>
       </c>
       <c r="G56">
         <v>3.48</v>
@@ -6132,45 +6132,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M56">
-        <v>1.36356912</v>
+        <v>1.4641528</v>
       </c>
       <c r="N56">
-        <v>2.050875324444444</v>
+        <v>1.950291644444444</v>
       </c>
       <c r="O56">
-        <v>0.6152625973333331</v>
+        <v>0.5850874933333331</v>
       </c>
       <c r="P56">
-        <v>1.435612727111111</v>
+        <v>1.365204151111111</v>
       </c>
       <c r="Q56">
-        <v>3.565612727111111</v>
+        <v>3.495204151111111</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2066993855933534</v>
+        <v>0.2096861151058262</v>
       </c>
       <c r="T56">
-        <v>1.121861723159695</v>
+        <v>1.142686523112274</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.504049405610215</v>
+        <v>2.332027397990458</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6178,22 +6178,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1235417517976218</v>
+        <v>0.123349386222301</v>
       </c>
       <c r="C57">
-        <v>22.14613353484574</v>
+        <v>21.88915033429787</v>
       </c>
       <c r="D57">
-        <v>37.98213353484574</v>
+        <v>38.07635033429787</v>
       </c>
       <c r="E57">
-        <v>10.596</v>
+        <v>10.9472</v>
       </c>
       <c r="F57">
-        <v>19.316</v>
+        <v>19.6672</v>
       </c>
       <c r="G57">
         <v>3.48</v>
@@ -6214,28 +6214,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M57">
-        <v>1.4641528</v>
+        <v>1.49077376</v>
       </c>
       <c r="N57">
-        <v>1.950291644444444</v>
+        <v>1.923670684444444</v>
       </c>
       <c r="O57">
-        <v>0.5850874933333331</v>
+        <v>0.5771012053333331</v>
       </c>
       <c r="P57">
-        <v>1.365204151111111</v>
+        <v>1.346569479111111</v>
       </c>
       <c r="Q57">
-        <v>3.495204151111111</v>
+        <v>3.476569479111111</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2096861151058262</v>
+        <v>0.2128086050506841</v>
       </c>
       <c r="T57">
-        <v>1.142686523112274</v>
+        <v>1.164457904880881</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.332027397990458</v>
+        <v>2.290384051597771</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6260,22 +6260,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.123349386222301</v>
+        <v>0.1231570206469802</v>
       </c>
       <c r="C58">
-        <v>21.88915033429787</v>
+        <v>21.63263571614058</v>
       </c>
       <c r="D58">
-        <v>38.07635033429787</v>
+        <v>38.17103571614058</v>
       </c>
       <c r="E58">
-        <v>10.9472</v>
+        <v>11.2984</v>
       </c>
       <c r="F58">
-        <v>19.6672</v>
+        <v>20.0184</v>
       </c>
       <c r="G58">
         <v>3.48</v>
@@ -6296,28 +6296,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M58">
-        <v>1.49077376</v>
+        <v>1.51739472</v>
       </c>
       <c r="N58">
-        <v>1.923670684444444</v>
+        <v>1.897049724444444</v>
       </c>
       <c r="O58">
-        <v>0.5771012053333331</v>
+        <v>0.5691149173333331</v>
       </c>
       <c r="P58">
-        <v>1.346569479111111</v>
+        <v>1.327934807111111</v>
       </c>
       <c r="Q58">
-        <v>3.476569479111111</v>
+        <v>3.457934807111111</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2128086050506841</v>
+        <v>0.2160763270860004</v>
       </c>
       <c r="T58">
-        <v>1.164457904880881</v>
+        <v>1.187241909057329</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.290384051597771</v>
+        <v>2.250201875253951</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6342,22 +6342,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1231570206469802</v>
+        <v>0.1229646550716594</v>
       </c>
       <c r="C59">
-        <v>21.63263571614058</v>
+        <v>21.3765931847939</v>
       </c>
       <c r="D59">
-        <v>38.17103571614058</v>
+        <v>38.26619318479391</v>
       </c>
       <c r="E59">
-        <v>11.2984</v>
+        <v>11.6496</v>
       </c>
       <c r="F59">
-        <v>20.0184</v>
+        <v>20.3696</v>
       </c>
       <c r="G59">
         <v>3.48</v>
@@ -6378,28 +6378,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M59">
-        <v>1.51739472</v>
+        <v>1.54401568</v>
       </c>
       <c r="N59">
-        <v>1.897049724444444</v>
+        <v>1.870428764444444</v>
       </c>
       <c r="O59">
-        <v>0.5691149173333331</v>
+        <v>0.5611286293333331</v>
       </c>
       <c r="P59">
-        <v>1.327934807111111</v>
+        <v>1.309300135111111</v>
       </c>
       <c r="Q59">
-        <v>3.457934807111111</v>
+        <v>3.439300135111111</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2160763270860004</v>
+        <v>0.2194996549325224</v>
       </c>
       <c r="T59">
-        <v>1.187241909057329</v>
+        <v>1.211110865813608</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.250201875253951</v>
+        <v>2.211405291197848</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6424,22 +6424,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1229646550716594</v>
+        <v>0.1227722894963386</v>
       </c>
       <c r="C60">
-        <v>21.3765931847939</v>
+        <v>21.12102627971023</v>
       </c>
       <c r="D60">
-        <v>38.26619318479391</v>
+        <v>38.36182627971023</v>
       </c>
       <c r="E60">
-        <v>11.6496</v>
+        <v>12.0008</v>
       </c>
       <c r="F60">
-        <v>20.3696</v>
+        <v>20.7208</v>
       </c>
       <c r="G60">
         <v>3.48</v>
@@ -6460,28 +6460,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M60">
-        <v>1.54401568</v>
+        <v>1.57063664</v>
       </c>
       <c r="N60">
-        <v>1.870428764444444</v>
+        <v>1.843807804444444</v>
       </c>
       <c r="O60">
-        <v>0.5611286293333332</v>
+        <v>0.5531423413333332</v>
       </c>
       <c r="P60">
-        <v>1.309300135111111</v>
+        <v>1.290665463111111</v>
       </c>
       <c r="Q60">
-        <v>3.439300135111111</v>
+        <v>3.420665463111111</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2194996549325223</v>
+        <v>0.2230899743813136</v>
       </c>
       <c r="T60">
-        <v>1.211110865813608</v>
+        <v>1.236144161923852</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.211405291197848</v>
+        <v>2.173923845584326</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6506,22 +6506,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1227722894963386</v>
+        <v>0.1225799239210178</v>
       </c>
       <c r="C61">
-        <v>21.12102627971023</v>
+        <v>20.86593857581309</v>
       </c>
       <c r="D61">
-        <v>38.36182627971023</v>
+        <v>38.45793857581309</v>
       </c>
       <c r="E61">
-        <v>12.0008</v>
+        <v>12.352</v>
       </c>
       <c r="F61">
-        <v>20.7208</v>
+        <v>21.072</v>
       </c>
       <c r="G61">
         <v>3.48</v>
@@ -6542,28 +6542,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M61">
-        <v>1.57063664</v>
+        <v>1.5972576</v>
       </c>
       <c r="N61">
-        <v>1.843807804444444</v>
+        <v>1.817186844444444</v>
       </c>
       <c r="O61">
-        <v>0.5531423413333332</v>
+        <v>0.5451560533333332</v>
       </c>
       <c r="P61">
-        <v>1.290665463111111</v>
+        <v>1.272030791111111</v>
       </c>
       <c r="Q61">
-        <v>3.420665463111111</v>
+        <v>3.402030791111111</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2230899743813136</v>
+        <v>0.2268598098025445</v>
       </c>
       <c r="T61">
-        <v>1.236144161923852</v>
+        <v>1.262429122839609</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.173923845584326</v>
+        <v>2.137691781491253</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6588,22 +6588,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1225799239210178</v>
+        <v>0.122387558345697</v>
       </c>
       <c r="C62">
-        <v>20.86593857581309</v>
+        <v>20.61133368394274</v>
       </c>
       <c r="D62">
-        <v>38.45793857581309</v>
+        <v>38.55453368394274</v>
       </c>
       <c r="E62">
-        <v>12.352</v>
+        <v>12.7032</v>
       </c>
       <c r="F62">
-        <v>21.072</v>
+        <v>21.4232</v>
       </c>
       <c r="G62">
         <v>3.48</v>
@@ -6624,28 +6624,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M62">
-        <v>1.5972576</v>
+        <v>1.62387856</v>
       </c>
       <c r="N62">
-        <v>1.817186844444444</v>
+        <v>1.790565884444444</v>
       </c>
       <c r="O62">
-        <v>0.5451560533333332</v>
+        <v>0.5371697653333332</v>
       </c>
       <c r="P62">
-        <v>1.272030791111111</v>
+        <v>1.253396119111111</v>
       </c>
       <c r="Q62">
-        <v>3.402030791111111</v>
+        <v>3.383396119111111</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2268598098025445</v>
+        <v>0.2308229701171718</v>
       </c>
       <c r="T62">
-        <v>1.262429122839609</v>
+        <v>1.290062030468993</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.137691781491253</v>
+        <v>2.102647653925823</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6670,22 +6670,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.122387558345697</v>
+        <v>0.1221951927703762</v>
       </c>
       <c r="C63">
-        <v>20.61133368394274</v>
+        <v>20.35721525130823</v>
       </c>
       <c r="D63">
-        <v>38.55453368394274</v>
+        <v>38.65161525130823</v>
       </c>
       <c r="E63">
-        <v>12.7032</v>
+        <v>13.0544</v>
       </c>
       <c r="F63">
-        <v>21.4232</v>
+        <v>21.7744</v>
       </c>
       <c r="G63">
         <v>3.48</v>
@@ -6706,28 +6706,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M63">
-        <v>1.62387856</v>
+        <v>1.65049952</v>
       </c>
       <c r="N63">
-        <v>1.790565884444444</v>
+        <v>1.763944924444444</v>
       </c>
       <c r="O63">
-        <v>0.5371697653333332</v>
+        <v>0.5291834773333332</v>
       </c>
       <c r="P63">
-        <v>1.253396119111111</v>
+        <v>1.234761447111111</v>
       </c>
       <c r="Q63">
-        <v>3.383396119111111</v>
+        <v>3.364761447111111</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2308229701171718</v>
+        <v>0.2349947178167794</v>
       </c>
       <c r="T63">
-        <v>1.290062030468993</v>
+        <v>1.319149301657819</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.102647653925823</v>
+        <v>2.06873398208831</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6752,22 +6752,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1221951927703762</v>
+        <v>0.1220028271950554</v>
       </c>
       <c r="C64">
-        <v>20.35721525130823</v>
+        <v>20.10358696194653</v>
       </c>
       <c r="D64">
-        <v>38.65161525130823</v>
+        <v>38.74918696194653</v>
       </c>
       <c r="E64">
-        <v>13.0544</v>
+        <v>13.4056</v>
       </c>
       <c r="F64">
-        <v>21.7744</v>
+        <v>22.1256</v>
       </c>
       <c r="G64">
         <v>3.48</v>
@@ -6788,28 +6788,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M64">
-        <v>1.65049952</v>
+        <v>1.67712048</v>
       </c>
       <c r="N64">
-        <v>1.763944924444444</v>
+        <v>1.737323964444444</v>
       </c>
       <c r="O64">
-        <v>0.5291834773333332</v>
+        <v>0.5211971893333331</v>
       </c>
       <c r="P64">
-        <v>1.234761447111111</v>
+        <v>1.216126775111111</v>
       </c>
       <c r="Q64">
-        <v>3.364761447111111</v>
+        <v>3.346126775111111</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2349947178167794</v>
+        <v>0.2393919653920416</v>
       </c>
       <c r="T64">
-        <v>1.319149301657819</v>
+        <v>1.349808857775771</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.06873398208831</v>
+        <v>2.035896934753574</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6834,22 +6834,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1220028271950554</v>
+        <v>0.1218104616197346</v>
       </c>
       <c r="C65">
-        <v>20.10358696194653</v>
+        <v>19.85045253718851</v>
       </c>
       <c r="D65">
-        <v>38.74918696194653</v>
+        <v>38.84725253718851</v>
       </c>
       <c r="E65">
-        <v>13.4056</v>
+        <v>13.7568</v>
       </c>
       <c r="F65">
-        <v>22.1256</v>
+        <v>22.4768</v>
       </c>
       <c r="G65">
         <v>3.48</v>
@@ -6870,28 +6870,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M65">
-        <v>1.67712048</v>
+        <v>1.70374144</v>
       </c>
       <c r="N65">
-        <v>1.737323964444444</v>
+        <v>1.710703004444444</v>
       </c>
       <c r="O65">
-        <v>0.5211971893333331</v>
+        <v>0.5132109013333331</v>
       </c>
       <c r="P65">
-        <v>1.216126775111111</v>
+        <v>1.197492103111111</v>
       </c>
       <c r="Q65">
-        <v>3.346126775111111</v>
+        <v>3.327492103111111</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2393919653920416</v>
+        <v>0.2440335044992628</v>
       </c>
       <c r="T65">
-        <v>1.349808857775771</v>
+        <v>1.382171722566943</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.035896934753574</v>
+        <v>2.00408604514805</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6916,22 +6916,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1218104616197346</v>
+        <v>0.1280790960444138</v>
       </c>
       <c r="C66">
-        <v>19.85045253718851</v>
+        <v>16.53957946995675</v>
       </c>
       <c r="D66">
-        <v>38.84725253718851</v>
+        <v>35.88757946995675</v>
       </c>
       <c r="E66">
-        <v>13.7568</v>
+        <v>14.108</v>
       </c>
       <c r="F66">
-        <v>22.4768</v>
+        <v>22.828</v>
       </c>
       <c r="G66">
         <v>3.48</v>
@@ -6952,45 +6952,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M66">
-        <v>1.70374144</v>
+        <v>2.05452</v>
       </c>
       <c r="N66">
-        <v>1.710703004444444</v>
+        <v>1.359924444444444</v>
       </c>
       <c r="O66">
-        <v>0.5132109013333331</v>
+        <v>0.4079773333333332</v>
       </c>
       <c r="P66">
-        <v>1.197492103111111</v>
+        <v>0.9519471111111111</v>
       </c>
       <c r="Q66">
-        <v>3.327492103111111</v>
+        <v>3.081947111111111</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2440335044992628</v>
+        <v>0.2489402744126109</v>
       </c>
       <c r="T66">
-        <v>1.382171722566943</v>
+        <v>1.416383893917609</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.00408604514805</v>
+        <v>1.661918328584995</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6998,22 +6998,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1280790960444138</v>
+        <v>0.127986130469093</v>
       </c>
       <c r="C67">
-        <v>16.53957946995675</v>
+        <v>16.22897402591471</v>
       </c>
       <c r="D67">
-        <v>35.88757946995675</v>
+        <v>35.92817402591471</v>
       </c>
       <c r="E67">
-        <v>14.108</v>
+        <v>14.4592</v>
       </c>
       <c r="F67">
-        <v>22.828</v>
+        <v>23.1792</v>
       </c>
       <c r="G67">
         <v>3.48</v>
@@ -7034,28 +7034,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M67">
-        <v>2.05452</v>
+        <v>2.086128</v>
       </c>
       <c r="N67">
-        <v>1.359924444444444</v>
+        <v>1.328316444444444</v>
       </c>
       <c r="O67">
-        <v>0.4079773333333332</v>
+        <v>0.3984949333333333</v>
       </c>
       <c r="P67">
-        <v>0.9519471111111111</v>
+        <v>0.9298215111111111</v>
       </c>
       <c r="Q67">
-        <v>3.081947111111111</v>
+        <v>3.059821511111112</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2489402744126109</v>
+        <v>0.2541356778502735</v>
       </c>
       <c r="T67">
-        <v>1.416383893917609</v>
+        <v>1.452608545935963</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.661918328584995</v>
+        <v>1.636737747848859</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7080,22 +7080,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.127986130469093</v>
+        <v>0.1278931648937722</v>
       </c>
       <c r="C68">
-        <v>16.22897402591471</v>
+        <v>15.91846052366231</v>
       </c>
       <c r="D68">
-        <v>35.92817402591471</v>
+        <v>35.96886052366231</v>
       </c>
       <c r="E68">
-        <v>14.4592</v>
+        <v>14.8104</v>
       </c>
       <c r="F68">
-        <v>23.1792</v>
+        <v>23.5304</v>
       </c>
       <c r="G68">
         <v>3.48</v>
@@ -7116,28 +7116,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M68">
-        <v>2.086128</v>
+        <v>2.117736</v>
       </c>
       <c r="N68">
-        <v>1.328316444444444</v>
+        <v>1.296708444444444</v>
       </c>
       <c r="O68">
-        <v>0.3984949333333333</v>
+        <v>0.3890125333333332</v>
       </c>
       <c r="P68">
-        <v>0.9298215111111111</v>
+        <v>0.9076959111111109</v>
       </c>
       <c r="Q68">
-        <v>3.059821511111112</v>
+        <v>3.037695911111111</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2541356778502735</v>
+        <v>0.2596459542235522</v>
       </c>
       <c r="T68">
-        <v>1.452608545935963</v>
+        <v>1.491028631409974</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.636737747848859</v>
+        <v>1.612308826239174</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7162,22 +7162,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1278931648937722</v>
+        <v>0.1278001993184514</v>
       </c>
       <c r="C69">
-        <v>15.91846052366231</v>
+        <v>15.60803927590937</v>
       </c>
       <c r="D69">
-        <v>35.96886052366231</v>
+        <v>36.00963927590937</v>
       </c>
       <c r="E69">
-        <v>14.8104</v>
+        <v>15.1616</v>
       </c>
       <c r="F69">
-        <v>23.5304</v>
+        <v>23.8816</v>
       </c>
       <c r="G69">
         <v>3.48</v>
@@ -7198,28 +7198,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M69">
-        <v>2.117736</v>
+        <v>2.149344</v>
       </c>
       <c r="N69">
-        <v>1.296708444444444</v>
+        <v>1.265100444444444</v>
       </c>
       <c r="O69">
-        <v>0.3890125333333332</v>
+        <v>0.3795301333333332</v>
       </c>
       <c r="P69">
-        <v>0.9076959111111109</v>
+        <v>0.8855703111111111</v>
       </c>
       <c r="Q69">
-        <v>3.037695911111111</v>
+        <v>3.015570311111111</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2596459542235522</v>
+        <v>0.2655006228701607</v>
       </c>
       <c r="T69">
-        <v>1.491028631409974</v>
+        <v>1.531849972226111</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.612308826239174</v>
+        <v>1.588598402323893</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7244,22 +7244,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1278001993184514</v>
+        <v>0.1277072337431306</v>
       </c>
       <c r="C70">
-        <v>15.60803927590937</v>
+        <v>15.29771059678534</v>
       </c>
       <c r="D70">
-        <v>36.00963927590937</v>
+        <v>36.05051059678534</v>
       </c>
       <c r="E70">
-        <v>15.1616</v>
+        <v>15.5128</v>
       </c>
       <c r="F70">
-        <v>23.8816</v>
+        <v>24.2328</v>
       </c>
       <c r="G70">
         <v>3.48</v>
@@ -7280,28 +7280,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M70">
-        <v>2.149344</v>
+        <v>2.180952</v>
       </c>
       <c r="N70">
-        <v>1.265100444444444</v>
+        <v>1.233492444444444</v>
       </c>
       <c r="O70">
-        <v>0.3795301333333332</v>
+        <v>0.3700477333333332</v>
       </c>
       <c r="P70">
-        <v>0.8855703111111111</v>
+        <v>0.8634447111111108</v>
       </c>
       <c r="Q70">
-        <v>3.015570311111111</v>
+        <v>2.993444711111111</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2655006228701607</v>
+        <v>0.2717330120746149</v>
       </c>
       <c r="T70">
-        <v>1.531849972226111</v>
+        <v>1.575304947933611</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.588598402323893</v>
+        <v>1.565575237072821</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7326,22 +7326,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1277072337431306</v>
+        <v>0.1276142681678098</v>
       </c>
       <c r="C71">
-        <v>15.29771059678534</v>
+        <v>14.98747480184752</v>
       </c>
       <c r="D71">
-        <v>36.05051059678534</v>
+        <v>36.09147480184753</v>
       </c>
       <c r="E71">
-        <v>15.5128</v>
+        <v>15.864</v>
       </c>
       <c r="F71">
-        <v>24.2328</v>
+        <v>24.584</v>
       </c>
       <c r="G71">
         <v>3.48</v>
@@ -7362,28 +7362,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M71">
-        <v>2.180952</v>
+        <v>2.21256</v>
       </c>
       <c r="N71">
-        <v>1.233492444444444</v>
+        <v>1.201884444444444</v>
       </c>
       <c r="O71">
-        <v>0.3700477333333332</v>
+        <v>0.3605653333333332</v>
       </c>
       <c r="P71">
-        <v>0.8634447111111108</v>
+        <v>0.8413191111111109</v>
       </c>
       <c r="Q71">
-        <v>2.993444711111111</v>
+        <v>2.971319111111111</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2717330120746149</v>
+        <v>0.2783808938926994</v>
       </c>
       <c r="T71">
-        <v>1.575304947933611</v>
+        <v>1.621656922021611</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.565575237072821</v>
+        <v>1.54320987654321</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7408,22 +7408,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1276142681678098</v>
+        <v>0.127521302592489</v>
       </c>
       <c r="C72">
-        <v>14.98747480184752</v>
+        <v>14.6773322080891</v>
       </c>
       <c r="D72">
-        <v>36.09147480184753</v>
+        <v>36.1325322080891</v>
       </c>
       <c r="E72">
-        <v>15.864</v>
+        <v>16.2152</v>
       </c>
       <c r="F72">
-        <v>24.584</v>
+        <v>24.9352</v>
       </c>
       <c r="G72">
         <v>3.48</v>
@@ -7444,28 +7444,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M72">
-        <v>2.21256</v>
+        <v>2.244168</v>
       </c>
       <c r="N72">
-        <v>1.201884444444444</v>
+        <v>1.170276444444444</v>
       </c>
       <c r="O72">
-        <v>0.3605653333333332</v>
+        <v>0.3510829333333331</v>
       </c>
       <c r="P72">
-        <v>0.8413191111111109</v>
+        <v>0.8191935111111106</v>
       </c>
       <c r="Q72">
-        <v>2.971319111111111</v>
+        <v>2.949193511111111</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2783808938926994</v>
+        <v>0.2854872503189277</v>
       </c>
       <c r="T72">
-        <v>1.621656922021611</v>
+        <v>1.67120558397775</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.54320987654321</v>
+        <v>1.521474526169361</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7490,22 +7490,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.127521302592489</v>
+        <v>0.1274283370171682</v>
       </c>
       <c r="C73">
-        <v>14.67733220808909</v>
+        <v>14.36728313394731</v>
       </c>
       <c r="D73">
-        <v>36.13253220808909</v>
+        <v>36.17368313394731</v>
       </c>
       <c r="E73">
-        <v>16.2152</v>
+        <v>16.56639999999999</v>
       </c>
       <c r="F73">
-        <v>24.9352</v>
+        <v>25.2864</v>
       </c>
       <c r="G73">
         <v>3.48</v>
@@ -7526,28 +7526,28 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M73">
-        <v>2.244168</v>
+        <v>2.275776</v>
       </c>
       <c r="N73">
-        <v>1.170276444444444</v>
+        <v>1.138668444444444</v>
       </c>
       <c r="O73">
-        <v>0.3510829333333332</v>
+        <v>0.3416005333333333</v>
       </c>
       <c r="P73">
-        <v>0.8191935111111111</v>
+        <v>0.7970679111111111</v>
       </c>
       <c r="Q73">
-        <v>2.949193511111111</v>
+        <v>2.927067911111112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2854872503189276</v>
+        <v>0.2931012036327436</v>
       </c>
       <c r="T73">
-        <v>1.671205583977749</v>
+        <v>1.724293436073612</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.521474526169362</v>
+        <v>1.500342935528121</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7572,22 +7572,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1274283370171682</v>
+        <v>0.1611371386093772</v>
       </c>
       <c r="C74">
-        <v>14.36728313394731</v>
+        <v>3.443846625189938</v>
       </c>
       <c r="D74">
-        <v>36.17368313394731</v>
+        <v>25.60144662518994</v>
       </c>
       <c r="E74">
-        <v>16.56639999999999</v>
+        <v>16.9176</v>
       </c>
       <c r="F74">
-        <v>25.2864</v>
+        <v>25.6376</v>
       </c>
       <c r="G74">
         <v>3.48</v>
@@ -7608,45 +7608,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M74">
-        <v>2.275776</v>
+        <v>3.76359968</v>
       </c>
       <c r="N74">
-        <v>1.138668444444444</v>
+        <v>-0.3491552355555561</v>
       </c>
       <c r="O74">
-        <v>0.3416005333333333</v>
+        <v>-0.1047465706666668</v>
       </c>
       <c r="P74">
-        <v>0.7970679111111111</v>
+        <v>-0.2444086648888892</v>
       </c>
       <c r="Q74">
-        <v>2.927067911111112</v>
+        <v>1.885591335111111</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2931012036327436</v>
+        <v>0.3079252047260884</v>
       </c>
       <c r="T74">
-        <v>1.724293436073612</v>
+        <v>1.827652932129934</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.3</v>
+        <v>0.2721685143020666</v>
       </c>
       <c r="W74">
-        <v>0.063</v>
+        <v>0.1068456621004566</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.500342935528121</v>
+        <v>0.9072283810068886</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7654,22 +7654,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1611371386093772</v>
+        <v>0.1621471386093772</v>
       </c>
       <c r="C75">
-        <v>3.443846625189938</v>
+        <v>2.870402559710548</v>
       </c>
       <c r="D75">
-        <v>25.60144662518994</v>
+        <v>25.37920255971055</v>
       </c>
       <c r="E75">
-        <v>16.9176</v>
+        <v>17.2688</v>
       </c>
       <c r="F75">
-        <v>25.6376</v>
+        <v>25.9888</v>
       </c>
       <c r="G75">
         <v>3.48</v>
@@ -7690,37 +7690,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M75">
-        <v>3.76359968</v>
+        <v>3.81515584</v>
       </c>
       <c r="N75">
-        <v>-0.3491552355555561</v>
+        <v>-0.4007113955555561</v>
       </c>
       <c r="O75">
-        <v>-0.1047465706666668</v>
+        <v>-0.1202134186666668</v>
       </c>
       <c r="P75">
-        <v>-0.2444086648888892</v>
+        <v>-0.2804979768888893</v>
       </c>
       <c r="Q75">
-        <v>1.885591335111111</v>
+        <v>1.849502023111111</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3079252047260884</v>
+        <v>0.3180069433693996</v>
       </c>
       <c r="T75">
-        <v>1.827652932129934</v>
+        <v>1.897947275673394</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2721685143020666</v>
+        <v>0.2684905614060927</v>
       </c>
       <c r="W75">
-        <v>0.1068456621004566</v>
+        <v>0.1073855855855856</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9072283810068886</v>
+        <v>0.894968538020309</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7736,22 +7736,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1621471386093772</v>
+        <v>0.1631571386093773</v>
       </c>
       <c r="C76">
-        <v>2.870402559710548</v>
+        <v>2.30078385174744</v>
       </c>
       <c r="D76">
-        <v>25.37920255971055</v>
+        <v>25.16078385174744</v>
       </c>
       <c r="E76">
-        <v>17.2688</v>
+        <v>17.62</v>
       </c>
       <c r="F76">
-        <v>25.9888</v>
+        <v>26.34</v>
       </c>
       <c r="G76">
         <v>3.48</v>
@@ -7772,37 +7772,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M76">
-        <v>3.81515584</v>
+        <v>3.866712</v>
       </c>
       <c r="N76">
-        <v>-0.4007113955555561</v>
+        <v>-0.4522675555555558</v>
       </c>
       <c r="O76">
-        <v>-0.1202134186666668</v>
+        <v>-0.1356802666666667</v>
       </c>
       <c r="P76">
-        <v>-0.2804979768888893</v>
+        <v>-0.316587288888889</v>
       </c>
       <c r="Q76">
-        <v>1.849502023111111</v>
+        <v>1.813412711111111</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3180069433693996</v>
+        <v>0.3288952211041756</v>
       </c>
       <c r="T76">
-        <v>1.897947275673394</v>
+        <v>1.97386516670033</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2684905614060927</v>
+        <v>0.2649106872540115</v>
       </c>
       <c r="W76">
-        <v>0.1073855855855856</v>
+        <v>0.1079111111111111</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.894968538020309</v>
+        <v>0.8830356241800383</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7818,22 +7818,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1631571386093773</v>
+        <v>0.1641671386093773</v>
       </c>
       <c r="C77">
-        <v>2.30078385174744</v>
+        <v>1.734892578571284</v>
       </c>
       <c r="D77">
-        <v>25.16078385174744</v>
+        <v>24.94609257857128</v>
       </c>
       <c r="E77">
-        <v>17.62</v>
+        <v>17.9712</v>
       </c>
       <c r="F77">
-        <v>26.34</v>
+        <v>26.6912</v>
       </c>
       <c r="G77">
         <v>3.48</v>
@@ -7854,37 +7854,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M77">
-        <v>3.866712</v>
+        <v>3.91826816</v>
       </c>
       <c r="N77">
-        <v>-0.4522675555555558</v>
+        <v>-0.5038237155555563</v>
       </c>
       <c r="O77">
-        <v>-0.1356802666666667</v>
+        <v>-0.1511471146666669</v>
       </c>
       <c r="P77">
-        <v>-0.316587288888889</v>
+        <v>-0.3526766008888894</v>
       </c>
       <c r="Q77">
-        <v>1.813412711111111</v>
+        <v>1.777323399111111</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3288952211041756</v>
+        <v>0.3406908553168496</v>
       </c>
       <c r="T77">
-        <v>1.97386516670033</v>
+        <v>2.056109548646177</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2649106872540115</v>
+        <v>0.2614250203164586</v>
       </c>
       <c r="W77">
-        <v>0.1079111111111111</v>
+        <v>0.1084228070175439</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8830356241800383</v>
+        <v>0.8714167343881956</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1641671386093773</v>
+        <v>0.1651771386093772</v>
       </c>
       <c r="C78">
-        <v>1.734892578571284</v>
+        <v>1.172634131385674</v>
       </c>
       <c r="D78">
-        <v>24.94609257857128</v>
+        <v>24.73503413138567</v>
       </c>
       <c r="E78">
-        <v>17.9712</v>
+        <v>18.32239999999999</v>
       </c>
       <c r="F78">
-        <v>26.6912</v>
+        <v>27.0424</v>
       </c>
       <c r="G78">
         <v>3.48</v>
@@ -7936,37 +7936,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M78">
-        <v>3.91826816</v>
+        <v>3.96982432</v>
       </c>
       <c r="N78">
-        <v>-0.5038237155555563</v>
+        <v>-0.5553798755555559</v>
       </c>
       <c r="O78">
-        <v>-0.1511471146666669</v>
+        <v>-0.1666139626666668</v>
       </c>
       <c r="P78">
-        <v>-0.3526766008888894</v>
+        <v>-0.3887659128888892</v>
       </c>
       <c r="Q78">
-        <v>1.777323399111111</v>
+        <v>1.741234087111111</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3406908553168496</v>
+        <v>0.3535121968523648</v>
       </c>
       <c r="T78">
-        <v>2.056109548646177</v>
+        <v>2.145505615978619</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2614250203164586</v>
+        <v>0.2580298901824787</v>
       </c>
       <c r="W78">
-        <v>0.1084228070175439</v>
+        <v>0.1089212121212121</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8714167343881956</v>
+        <v>0.8600996339415957</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7982,22 +7982,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1651771386093772</v>
+        <v>0.1661871386093772</v>
       </c>
       <c r="C79">
-        <v>1.172634131385674</v>
+        <v>0.6139170763142019</v>
       </c>
       <c r="D79">
-        <v>24.73503413138567</v>
+        <v>24.5275170763142</v>
       </c>
       <c r="E79">
-        <v>18.32239999999999</v>
+        <v>18.6736</v>
       </c>
       <c r="F79">
-        <v>27.0424</v>
+        <v>27.3936</v>
       </c>
       <c r="G79">
         <v>3.48</v>
@@ -8018,37 +8018,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M79">
-        <v>3.96982432</v>
+        <v>4.02138048</v>
       </c>
       <c r="N79">
-        <v>-0.5553798755555559</v>
+        <v>-0.6069360355555564</v>
       </c>
       <c r="O79">
-        <v>-0.1666139626666668</v>
+        <v>-0.1820808106666669</v>
       </c>
       <c r="P79">
-        <v>-0.3887659128888892</v>
+        <v>-0.4248552248888895</v>
       </c>
       <c r="Q79">
-        <v>1.741234087111111</v>
+        <v>1.705144775111111</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3535121968523648</v>
+        <v>0.3674991148911086</v>
       </c>
       <c r="T79">
-        <v>2.145505615978619</v>
+        <v>2.243028598523102</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2580298901824787</v>
+        <v>0.2547218146673187</v>
       </c>
       <c r="W79">
-        <v>0.1089212121212121</v>
+        <v>0.1094068376068376</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8600996339415957</v>
+        <v>0.849072715557729</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8064,22 +8064,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1661871386093772</v>
+        <v>0.1671971386093773</v>
       </c>
       <c r="C80">
-        <v>0.6139170763142019</v>
+        <v>0.058653022326979</v>
       </c>
       <c r="D80">
-        <v>24.5275170763142</v>
+        <v>24.32345302232698</v>
       </c>
       <c r="E80">
-        <v>18.6736</v>
+        <v>19.0248</v>
       </c>
       <c r="F80">
-        <v>27.3936</v>
+        <v>27.7448</v>
       </c>
       <c r="G80">
         <v>3.48</v>
@@ -8100,37 +8100,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M80">
-        <v>4.02138048</v>
+        <v>4.07293664</v>
       </c>
       <c r="N80">
-        <v>-0.6069360355555564</v>
+        <v>-0.658492195555556</v>
       </c>
       <c r="O80">
-        <v>-0.1820808106666669</v>
+        <v>-0.1975476586666668</v>
       </c>
       <c r="P80">
-        <v>-0.4248552248888895</v>
+        <v>-0.4609445368888893</v>
       </c>
       <c r="Q80">
-        <v>1.705144775111111</v>
+        <v>1.669055463111111</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3674991148911086</v>
+        <v>0.3828181203621139</v>
       </c>
       <c r="T80">
-        <v>2.243028598523102</v>
+        <v>2.34983948416706</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2547218146673187</v>
+        <v>0.2514974878993779</v>
       </c>
       <c r="W80">
-        <v>0.1094068376068376</v>
+        <v>0.1098801687763713</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.849072715557729</v>
+        <v>0.8383249596645932</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8146,22 +8146,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1671971386093773</v>
+        <v>0.1682071386093772</v>
       </c>
       <c r="C81">
-        <v>0.058653022326979</v>
+        <v>-0.4932435042942878</v>
       </c>
       <c r="D81">
-        <v>24.32345302232698</v>
+        <v>24.12275649570571</v>
       </c>
       <c r="E81">
-        <v>19.0248</v>
+        <v>19.376</v>
       </c>
       <c r="F81">
-        <v>27.7448</v>
+        <v>28.096</v>
       </c>
       <c r="G81">
         <v>3.48</v>
@@ -8182,37 +8182,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M81">
-        <v>4.07293664</v>
+        <v>4.124492800000001</v>
       </c>
       <c r="N81">
-        <v>-0.658492195555556</v>
+        <v>-0.7100483555555566</v>
       </c>
       <c r="O81">
-        <v>-0.1975476586666668</v>
+        <v>-0.213014506666667</v>
       </c>
       <c r="P81">
-        <v>-0.4609445368888893</v>
+        <v>-0.4970338488888896</v>
       </c>
       <c r="Q81">
-        <v>1.669055463111111</v>
+        <v>1.632966151111111</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3828181203621139</v>
+        <v>0.3996690263802196</v>
       </c>
       <c r="T81">
-        <v>2.34983948416706</v>
+        <v>2.467331458375412</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2514974878993779</v>
+        <v>0.2483537693006357</v>
       </c>
       <c r="W81">
-        <v>0.1098801687763713</v>
+        <v>0.1103416666666667</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8383249596645932</v>
+        <v>0.8278458976687857</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8228,22 +8228,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1682071386093772</v>
+        <v>0.1692171386093773</v>
       </c>
       <c r="C82">
-        <v>-0.4932435042942878</v>
+        <v>-1.041855179327335</v>
       </c>
       <c r="D82">
-        <v>24.12275649570571</v>
+        <v>23.92534482067266</v>
       </c>
       <c r="E82">
-        <v>19.376</v>
+        <v>19.7272</v>
       </c>
       <c r="F82">
-        <v>28.096</v>
+        <v>28.4472</v>
       </c>
       <c r="G82">
         <v>3.48</v>
@@ -8264,37 +8264,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M82">
-        <v>4.124492800000001</v>
+        <v>4.17604896</v>
       </c>
       <c r="N82">
-        <v>-0.7100483555555566</v>
+        <v>-0.7616045155555562</v>
       </c>
       <c r="O82">
-        <v>-0.213014506666667</v>
+        <v>-0.2284813546666669</v>
       </c>
       <c r="P82">
-        <v>-0.4970338488888896</v>
+        <v>-0.5331231608888893</v>
       </c>
       <c r="Q82">
-        <v>1.632966151111111</v>
+        <v>1.596876839111111</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3996690263802196</v>
+        <v>0.4182937119791785</v>
       </c>
       <c r="T82">
-        <v>2.467331458375412</v>
+        <v>2.597191008816224</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2483537693006357</v>
+        <v>0.2452876733833439</v>
       </c>
       <c r="W82">
-        <v>0.1103416666666667</v>
+        <v>0.1107917695473251</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8278458976687857</v>
+        <v>0.8176255779444799</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8310,22 +8310,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1692171386093773</v>
+        <v>0.1702271386093772</v>
       </c>
       <c r="C83">
-        <v>-1.041855179327335</v>
+        <v>-1.587261994166504</v>
       </c>
       <c r="D83">
-        <v>23.92534482067266</v>
+        <v>23.7311380058335</v>
       </c>
       <c r="E83">
-        <v>19.7272</v>
+        <v>20.0784</v>
       </c>
       <c r="F83">
-        <v>28.4472</v>
+        <v>28.7984</v>
       </c>
       <c r="G83">
         <v>3.48</v>
@@ -8346,37 +8346,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M83">
-        <v>4.17604896</v>
+        <v>4.227605120000001</v>
       </c>
       <c r="N83">
-        <v>-0.7616045155555562</v>
+        <v>-0.8131606755555567</v>
       </c>
       <c r="O83">
-        <v>-0.2284813546666669</v>
+        <v>-0.243948202666667</v>
       </c>
       <c r="P83">
-        <v>-0.5331231608888893</v>
+        <v>-0.5692124728888897</v>
       </c>
       <c r="Q83">
-        <v>1.596876839111111</v>
+        <v>1.560787527111111</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4182937119791785</v>
+        <v>0.4389878070891328</v>
       </c>
       <c r="T83">
-        <v>2.597191008816224</v>
+        <v>2.741479398194902</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2452876733833439</v>
+        <v>0.2422963602933031</v>
       </c>
       <c r="W83">
-        <v>0.1107917695473251</v>
+        <v>0.1112308943089431</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8176255779444799</v>
+        <v>0.8076545343110104</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8392,22 +8392,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1702271386093772</v>
+        <v>0.2207762365718672</v>
       </c>
       <c r="C84">
-        <v>-1.587261994166504</v>
+        <v>-8.794179337964465</v>
       </c>
       <c r="D84">
-        <v>23.7311380058335</v>
+        <v>16.87542066203553</v>
       </c>
       <c r="E84">
-        <v>20.0784</v>
+        <v>20.4296</v>
       </c>
       <c r="F84">
-        <v>28.7984</v>
+        <v>29.1496</v>
       </c>
       <c r="G84">
         <v>3.48</v>
@@ -8428,45 +8428,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M84">
-        <v>4.227605120000001</v>
+        <v>5.85323968</v>
       </c>
       <c r="N84">
-        <v>-0.8131606755555567</v>
+        <v>-2.438795235555556</v>
       </c>
       <c r="O84">
-        <v>-0.243948202666667</v>
+        <v>-0.7316385706666667</v>
       </c>
       <c r="P84">
-        <v>-0.5692124728888897</v>
+        <v>-1.707156664888889</v>
       </c>
       <c r="Q84">
-        <v>1.560787527111111</v>
+        <v>0.4228433351111112</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4389878070891328</v>
+        <v>0.4898759014031401</v>
       </c>
       <c r="T84">
-        <v>2.741479398194902</v>
+        <v>3.096293712524911</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.2422963602933031</v>
+        <v>0.1750028000448007</v>
       </c>
       <c r="W84">
-        <v>0.1112308943089431</v>
+        <v>0.165659437751004</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8076545343110104</v>
+        <v>0.5833426668160023</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8474,22 +8474,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2207762365718672</v>
+        <v>0.2223262365718672</v>
       </c>
       <c r="C85">
-        <v>-8.794179337964465</v>
+        <v>-9.293555056963079</v>
       </c>
       <c r="D85">
-        <v>16.87542066203553</v>
+        <v>16.72724494303692</v>
       </c>
       <c r="E85">
-        <v>20.4296</v>
+        <v>20.7808</v>
       </c>
       <c r="F85">
-        <v>29.1496</v>
+        <v>29.5008</v>
       </c>
       <c r="G85">
         <v>3.48</v>
@@ -8510,37 +8510,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M85">
-        <v>5.85323968</v>
+        <v>5.92376064</v>
       </c>
       <c r="N85">
-        <v>-2.438795235555556</v>
+        <v>-2.509316195555556</v>
       </c>
       <c r="O85">
-        <v>-0.7316385706666667</v>
+        <v>-0.7527948586666668</v>
       </c>
       <c r="P85">
-        <v>-1.707156664888889</v>
+        <v>-1.756521336888889</v>
       </c>
       <c r="Q85">
-        <v>0.4228433351111112</v>
+        <v>0.3734786631111109</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4898759014031401</v>
+        <v>0.5176306452408365</v>
       </c>
       <c r="T85">
-        <v>3.096293712524911</v>
+        <v>3.289812069557719</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1750028000448007</v>
+        <v>0.1729194333776007</v>
       </c>
       <c r="W85">
-        <v>0.165659437751004</v>
+        <v>0.1660777777777778</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5833426668160023</v>
+        <v>0.5763981112586689</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8556,22 +8556,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2223262365718671</v>
+        <v>0.2238762365718671</v>
       </c>
       <c r="C86">
-        <v>-9.293555056963072</v>
+        <v>-9.790351292377917</v>
       </c>
       <c r="D86">
-        <v>16.72724494303693</v>
+        <v>16.58164870762208</v>
       </c>
       <c r="E86">
-        <v>20.7808</v>
+        <v>21.132</v>
       </c>
       <c r="F86">
-        <v>29.5008</v>
+        <v>29.852</v>
       </c>
       <c r="G86">
         <v>3.48</v>
@@ -8592,37 +8592,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M86">
-        <v>5.92376064</v>
+        <v>5.9942816</v>
       </c>
       <c r="N86">
-        <v>-2.509316195555556</v>
+        <v>-2.579837155555556</v>
       </c>
       <c r="O86">
-        <v>-0.7527948586666668</v>
+        <v>-0.7739511466666668</v>
       </c>
       <c r="P86">
-        <v>-1.756521336888889</v>
+        <v>-1.805886008888889</v>
       </c>
       <c r="Q86">
-        <v>0.3734786631111109</v>
+        <v>0.3241139911111111</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5176306452408361</v>
+        <v>0.5490860215902251</v>
       </c>
       <c r="T86">
-        <v>3.289812069557716</v>
+        <v>3.509132874194897</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1729194333776007</v>
+        <v>0.1708850871025701</v>
       </c>
       <c r="W86">
-        <v>0.1660777777777778</v>
+        <v>0.1664862745098039</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5763981112586689</v>
+        <v>0.569616957008567</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8638,22 +8638,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2238762365718671</v>
+        <v>0.2254262365718672</v>
       </c>
       <c r="C87">
-        <v>-9.790351292377917</v>
+        <v>-10.28463481952475</v>
       </c>
       <c r="D87">
-        <v>16.58164870762208</v>
+        <v>16.43856518047524</v>
       </c>
       <c r="E87">
-        <v>21.132</v>
+        <v>21.4832</v>
       </c>
       <c r="F87">
-        <v>29.852</v>
+        <v>30.2032</v>
       </c>
       <c r="G87">
         <v>3.48</v>
@@ -8674,37 +8674,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M87">
-        <v>5.9942816</v>
+        <v>6.06480256</v>
       </c>
       <c r="N87">
-        <v>-2.579837155555556</v>
+        <v>-2.650358115555556</v>
       </c>
       <c r="O87">
-        <v>-0.7739511466666668</v>
+        <v>-0.7951074346666669</v>
       </c>
       <c r="P87">
-        <v>-1.805886008888889</v>
+        <v>-1.85525068088889</v>
       </c>
       <c r="Q87">
-        <v>0.3241139911111111</v>
+        <v>0.2747493191111108</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5490860215902251</v>
+        <v>0.5850350231323842</v>
       </c>
       <c r="T87">
-        <v>3.509132874194897</v>
+        <v>3.759785222351676</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1708850871025701</v>
+        <v>0.1688980512060285</v>
       </c>
       <c r="W87">
-        <v>0.1664862745098039</v>
+        <v>0.1668852713178295</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.569616957008567</v>
+        <v>0.5629935040200953</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8720,22 +8720,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2254262365718672</v>
+        <v>0.2269762365718671</v>
       </c>
       <c r="C88">
-        <v>-10.28463481952475</v>
+        <v>-10.77647012861303</v>
       </c>
       <c r="D88">
-        <v>16.43856518047524</v>
+        <v>16.29792987138696</v>
       </c>
       <c r="E88">
-        <v>21.4832</v>
+        <v>21.8344</v>
       </c>
       <c r="F88">
-        <v>30.2032</v>
+        <v>30.5544</v>
       </c>
       <c r="G88">
         <v>3.48</v>
@@ -8756,37 +8756,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M88">
-        <v>6.06480256</v>
+        <v>6.13532352</v>
       </c>
       <c r="N88">
-        <v>-2.650358115555556</v>
+        <v>-2.720879075555556</v>
       </c>
       <c r="O88">
-        <v>-0.7951074346666669</v>
+        <v>-0.8162637226666668</v>
       </c>
       <c r="P88">
-        <v>-1.85525068088889</v>
+        <v>-1.904615352888889</v>
       </c>
       <c r="Q88">
-        <v>0.2747493191111108</v>
+        <v>0.2253846471111109</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5850350231323842</v>
+        <v>0.6265146402964137</v>
       </c>
       <c r="T88">
-        <v>3.759785222351676</v>
+        <v>4.048999470224881</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1688980512060285</v>
+        <v>0.1669566942956144</v>
       </c>
       <c r="W88">
-        <v>0.1668852713178295</v>
+        <v>0.1672750957854406</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5629935040200953</v>
+        <v>0.5565223143187148</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8802,22 +8802,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2269762365718671</v>
+        <v>0.2285262365718672</v>
       </c>
       <c r="C89">
-        <v>-10.77647012861303</v>
+        <v>-11.26591952166456</v>
       </c>
       <c r="D89">
-        <v>16.29792987138696</v>
+        <v>16.15968047833544</v>
       </c>
       <c r="E89">
-        <v>21.8344</v>
+        <v>22.18559999999999</v>
       </c>
       <c r="F89">
-        <v>30.5544</v>
+        <v>30.9056</v>
       </c>
       <c r="G89">
         <v>3.48</v>
@@ -8838,37 +8838,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M89">
-        <v>6.13532352</v>
+        <v>6.20584448</v>
       </c>
       <c r="N89">
-        <v>-2.720879075555556</v>
+        <v>-2.791400035555556</v>
       </c>
       <c r="O89">
-        <v>-0.8162637226666668</v>
+        <v>-0.8374200106666667</v>
       </c>
       <c r="P89">
-        <v>-1.904615352888889</v>
+        <v>-1.953980024888889</v>
       </c>
       <c r="Q89">
-        <v>0.2253846471111109</v>
+        <v>0.1760199751111113</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6265146402964137</v>
+        <v>0.6749075269877817</v>
       </c>
       <c r="T89">
-        <v>4.048999470224881</v>
+        <v>4.386416092743623</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1669566942956144</v>
+        <v>0.1650594591331643</v>
       </c>
       <c r="W89">
-        <v>0.1672750957854406</v>
+        <v>0.1676560606060606</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5565223143187148</v>
+        <v>0.5501981971105476</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8884,22 +8884,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2285262365718672</v>
+        <v>0.2300762365718671</v>
       </c>
       <c r="C90">
-        <v>-11.26591952166456</v>
+        <v>-11.75304320454079</v>
       </c>
       <c r="D90">
-        <v>16.15968047833544</v>
+        <v>16.02375679545921</v>
       </c>
       <c r="E90">
-        <v>22.18559999999999</v>
+        <v>22.5368</v>
       </c>
       <c r="F90">
-        <v>30.9056</v>
+        <v>31.2568</v>
       </c>
       <c r="G90">
         <v>3.48</v>
@@ -8920,37 +8920,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M90">
-        <v>6.20584448</v>
+        <v>6.27636544</v>
       </c>
       <c r="N90">
-        <v>-2.791400035555556</v>
+        <v>-2.861920995555556</v>
       </c>
       <c r="O90">
-        <v>-0.8374200106666667</v>
+        <v>-0.8585762986666668</v>
       </c>
       <c r="P90">
-        <v>-1.953980024888889</v>
+        <v>-2.003344696888889</v>
       </c>
       <c r="Q90">
-        <v>0.1760199751111113</v>
+        <v>0.1266553031111108</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6749075269877817</v>
+        <v>0.7320991203503072</v>
       </c>
       <c r="T90">
-        <v>4.386416092743623</v>
+        <v>4.785181192083952</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1650594591331643</v>
+        <v>0.1632048584687467</v>
       </c>
       <c r="W90">
-        <v>0.1676560606060606</v>
+        <v>0.1680284644194757</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5501981971105476</v>
+        <v>0.5440161948958224</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8966,22 +8966,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2300762365718671</v>
+        <v>0.2316262365718671</v>
       </c>
       <c r="C91">
-        <v>-11.75304320454079</v>
+        <v>-12.23789937436456</v>
       </c>
       <c r="D91">
-        <v>16.02375679545921</v>
+        <v>15.89010062563544</v>
       </c>
       <c r="E91">
-        <v>22.5368</v>
+        <v>22.888</v>
       </c>
       <c r="F91">
-        <v>31.2568</v>
+        <v>31.608</v>
       </c>
       <c r="G91">
         <v>3.48</v>
@@ -9002,37 +9002,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M91">
-        <v>6.27636544</v>
+        <v>6.3468864</v>
       </c>
       <c r="N91">
-        <v>-2.861920995555556</v>
+        <v>-2.932441955555556</v>
       </c>
       <c r="O91">
-        <v>-0.8585762986666668</v>
+        <v>-0.8797325866666668</v>
       </c>
       <c r="P91">
-        <v>-2.003344696888889</v>
+        <v>-2.052709368888889</v>
       </c>
       <c r="Q91">
-        <v>0.1266553031111108</v>
+        <v>0.07729063111111101</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7320991203503072</v>
+        <v>0.800729032385338</v>
       </c>
       <c r="T91">
-        <v>4.785181192083952</v>
+        <v>5.263699311292347</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1632048584687467</v>
+        <v>0.1613914711524273</v>
       </c>
       <c r="W91">
-        <v>0.1680284644194757</v>
+        <v>0.1683925925925926</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5440161948958224</v>
+        <v>0.537971570508091</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9048,22 +9048,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2316262365718671</v>
+        <v>0.2331762365718671</v>
       </c>
       <c r="C92">
-        <v>-12.23789937436456</v>
+        <v>-12.72054430260278</v>
       </c>
       <c r="D92">
-        <v>15.89010062563544</v>
+        <v>15.75865569739722</v>
       </c>
       <c r="E92">
-        <v>22.888</v>
+        <v>23.2392</v>
       </c>
       <c r="F92">
-        <v>31.608</v>
+        <v>31.9592</v>
       </c>
       <c r="G92">
         <v>3.48</v>
@@ -9084,37 +9084,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M92">
-        <v>6.3468864</v>
+        <v>6.41740736</v>
       </c>
       <c r="N92">
-        <v>-2.932441955555556</v>
+        <v>-3.002962915555556</v>
       </c>
       <c r="O92">
-        <v>-0.8797325866666668</v>
+        <v>-0.9008888746666669</v>
       </c>
       <c r="P92">
-        <v>-2.052709368888889</v>
+        <v>-2.10207404088889</v>
       </c>
       <c r="Q92">
-        <v>0.07729063111111101</v>
+        <v>0.02792595911111073</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.800729032385338</v>
+        <v>0.884610035983709</v>
       </c>
       <c r="T92">
-        <v>5.263699311292347</v>
+        <v>5.848554790324831</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1613914711524273</v>
+        <v>0.1596179385024006</v>
       </c>
       <c r="W92">
-        <v>0.1683925925925926</v>
+        <v>0.168748717948718</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.537971570508091</v>
+        <v>0.5320597950080022</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9130,22 +9130,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2331762365718671</v>
+        <v>0.2347262365718671</v>
       </c>
       <c r="C93">
-        <v>-12.72054430260278</v>
+        <v>-13.2010324140593</v>
       </c>
       <c r="D93">
-        <v>15.75865569739722</v>
+        <v>15.6293675859407</v>
       </c>
       <c r="E93">
-        <v>23.2392</v>
+        <v>23.5904</v>
       </c>
       <c r="F93">
-        <v>31.9592</v>
+        <v>32.3104</v>
       </c>
       <c r="G93">
         <v>3.48</v>
@@ -9166,37 +9166,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M93">
-        <v>6.41740736</v>
+        <v>6.487928320000001</v>
       </c>
       <c r="N93">
-        <v>-3.002962915555556</v>
+        <v>-3.073483875555557</v>
       </c>
       <c r="O93">
-        <v>-0.9008888746666669</v>
+        <v>-0.922045162666667</v>
       </c>
       <c r="P93">
-        <v>-2.10207404088889</v>
+        <v>-2.15143871288889</v>
       </c>
       <c r="Q93">
-        <v>0.02792595911111073</v>
+        <v>-0.02143871288888954</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.884610035983709</v>
+        <v>0.989461290481673</v>
       </c>
       <c r="T93">
-        <v>5.848554790324831</v>
+        <v>6.579624139115437</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1596179385024006</v>
+        <v>0.1578829609099832</v>
       </c>
       <c r="W93">
-        <v>0.168748717948718</v>
+        <v>0.1690971014492754</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5320597950080022</v>
+        <v>0.5262765363666106</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9212,22 +9212,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2347262365718671</v>
+        <v>0.2362762365718671</v>
       </c>
       <c r="C94">
-        <v>-13.2010324140593</v>
+        <v>-13.67941636201109</v>
       </c>
       <c r="D94">
-        <v>15.6293675859407</v>
+        <v>15.50218363798891</v>
       </c>
       <c r="E94">
-        <v>23.5904</v>
+        <v>23.9416</v>
       </c>
       <c r="F94">
-        <v>32.3104</v>
+        <v>32.6616</v>
       </c>
       <c r="G94">
         <v>3.48</v>
@@ -9248,37 +9248,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M94">
-        <v>6.487928320000001</v>
+        <v>6.55844928</v>
       </c>
       <c r="N94">
-        <v>-3.073483875555557</v>
+        <v>-3.144004835555557</v>
       </c>
       <c r="O94">
-        <v>-0.922045162666667</v>
+        <v>-0.9432014506666669</v>
       </c>
       <c r="P94">
-        <v>-2.15143871288889</v>
+        <v>-2.20080338488889</v>
       </c>
       <c r="Q94">
-        <v>-0.02143871288888954</v>
+        <v>-0.07080338488888938</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.989461290481673</v>
+        <v>1.124270046264769</v>
       </c>
       <c r="T94">
-        <v>6.579624139115437</v>
+        <v>7.519570444703358</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1578829609099832</v>
+        <v>0.1561852946636393</v>
       </c>
       <c r="W94">
-        <v>0.1690971014492754</v>
+        <v>0.1694379928315412</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5262765363666106</v>
+        <v>0.5206176488787977</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9294,22 +9294,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2362762365718671</v>
+        <v>0.2378262365718671</v>
       </c>
       <c r="C95">
-        <v>-13.67941636201109</v>
+        <v>-14.15574709970531</v>
       </c>
       <c r="D95">
-        <v>15.50218363798891</v>
+        <v>15.37705290029469</v>
       </c>
       <c r="E95">
-        <v>23.9416</v>
+        <v>24.2928</v>
       </c>
       <c r="F95">
-        <v>32.6616</v>
+        <v>33.0128</v>
       </c>
       <c r="G95">
         <v>3.48</v>
@@ -9330,37 +9330,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M95">
-        <v>6.55844928</v>
+        <v>6.62897024</v>
       </c>
       <c r="N95">
-        <v>-3.144004835555557</v>
+        <v>-3.214525795555556</v>
       </c>
       <c r="O95">
-        <v>-0.9432014506666669</v>
+        <v>-0.9643577386666669</v>
       </c>
       <c r="P95">
-        <v>-2.20080338488889</v>
+        <v>-2.25016805688889</v>
       </c>
       <c r="Q95">
-        <v>-0.07080338488888938</v>
+        <v>-0.1201680568888892</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.124270046264769</v>
+        <v>1.304015053975564</v>
       </c>
       <c r="T95">
-        <v>7.519570444703358</v>
+        <v>8.772832185487252</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1561852946636393</v>
+        <v>0.1545237489757283</v>
       </c>
       <c r="W95">
-        <v>0.1694379928315412</v>
+        <v>0.1697716312056738</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5206176488787977</v>
+        <v>0.5150791632524275</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9376,22 +9376,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2378262365718671</v>
+        <v>0.2393762365718672</v>
       </c>
       <c r="C96">
-        <v>-14.15574709970531</v>
+        <v>-14.63007394842161</v>
       </c>
       <c r="D96">
-        <v>15.37705290029469</v>
+        <v>15.25392605157838</v>
       </c>
       <c r="E96">
-        <v>24.2928</v>
+        <v>24.644</v>
       </c>
       <c r="F96">
-        <v>33.0128</v>
+        <v>33.364</v>
       </c>
       <c r="G96">
         <v>3.48</v>
@@ -9412,37 +9412,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M96">
-        <v>6.62897024</v>
+        <v>6.6994912</v>
       </c>
       <c r="N96">
-        <v>-3.214525795555556</v>
+        <v>-3.285046755555556</v>
       </c>
       <c r="O96">
-        <v>-0.9643577386666669</v>
+        <v>-0.9855140266666667</v>
       </c>
       <c r="P96">
-        <v>-2.25016805688889</v>
+        <v>-2.299532728888889</v>
       </c>
       <c r="Q96">
-        <v>-0.1201680568888892</v>
+        <v>-0.1695327288888886</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.304015053975564</v>
+        <v>1.555658064770678</v>
       </c>
       <c r="T96">
-        <v>8.772832185487252</v>
+        <v>10.52739862258471</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1545237489757283</v>
+        <v>0.1528971831970364</v>
       </c>
       <c r="W96">
-        <v>0.1697716312056738</v>
+        <v>0.1700982456140351</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5150791632524275</v>
+        <v>0.5096572773234547</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9458,22 +9458,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2393762365718672</v>
+        <v>0.2409262365718672</v>
       </c>
       <c r="C97">
-        <v>-14.63007394842161</v>
+        <v>-15.10244466229043</v>
       </c>
       <c r="D97">
-        <v>15.25392605157838</v>
+        <v>15.13275533770957</v>
       </c>
       <c r="E97">
-        <v>24.644</v>
+        <v>24.9952</v>
       </c>
       <c r="F97">
-        <v>33.364</v>
+        <v>33.7152</v>
       </c>
       <c r="G97">
         <v>3.48</v>
@@ -9494,37 +9494,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M97">
-        <v>6.6994912</v>
+        <v>6.770012160000001</v>
       </c>
       <c r="N97">
-        <v>-3.285046755555556</v>
+        <v>-3.355567715555557</v>
       </c>
       <c r="O97">
-        <v>-0.9855140266666667</v>
+        <v>-1.006670314666667</v>
       </c>
       <c r="P97">
-        <v>-2.299532728888889</v>
+        <v>-2.34889740088889</v>
       </c>
       <c r="Q97">
-        <v>-0.1695327288888886</v>
+        <v>-0.2188974008888898</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.555658064770678</v>
+        <v>1.933122580963349</v>
       </c>
       <c r="T97">
-        <v>10.52739862258471</v>
+        <v>13.15924827823089</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1528971831970364</v>
+        <v>0.1513045042054006</v>
       </c>
       <c r="W97">
-        <v>0.1700982456140351</v>
+        <v>0.1704180555555556</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5096572773234547</v>
+        <v>0.5043483473513353</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9540,22 +9540,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2409262365718671</v>
+        <v>0.278330449600114</v>
       </c>
       <c r="C98">
-        <v>-15.10244466229042</v>
+        <v>-17.8878583548603</v>
       </c>
       <c r="D98">
-        <v>15.13275533770958</v>
+        <v>12.6985416451397</v>
       </c>
       <c r="E98">
-        <v>24.9952</v>
+        <v>25.3464</v>
       </c>
       <c r="F98">
-        <v>33.7152</v>
+        <v>34.06639999999999</v>
       </c>
       <c r="G98">
         <v>3.48</v>
@@ -9576,45 +9576,45 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M98">
-        <v>6.770012159999999</v>
+        <v>8.032857119999999</v>
       </c>
       <c r="N98">
-        <v>-3.355567715555555</v>
+        <v>-4.618412675555556</v>
       </c>
       <c r="O98">
-        <v>-1.006670314666667</v>
+        <v>-1.385523802666667</v>
       </c>
       <c r="P98">
-        <v>-2.348897400888889</v>
+        <v>-3.232888872888889</v>
       </c>
       <c r="Q98">
-        <v>-0.2188974008888884</v>
+        <v>-1.102888872888889</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.933122580963343</v>
+        <v>2.625703875559354</v>
       </c>
       <c r="T98">
-        <v>13.15924827823086</v>
+        <v>17.98823156936251</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1513045042054006</v>
+        <v>0.1275179326647022</v>
       </c>
       <c r="W98">
-        <v>0.1704180555555556</v>
+        <v>0.2057312714776632</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5043483473513354</v>
+        <v>0.4250597755490071</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9622,22 +9622,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.278330449600114</v>
+        <v>0.280230449600114</v>
       </c>
       <c r="C99">
-        <v>-17.8878583548603</v>
+        <v>-18.34197685016209</v>
       </c>
       <c r="D99">
-        <v>12.6985416451397</v>
+        <v>12.59562314983791</v>
       </c>
       <c r="E99">
-        <v>25.3464</v>
+        <v>25.6976</v>
       </c>
       <c r="F99">
-        <v>34.06639999999999</v>
+        <v>34.4176</v>
       </c>
       <c r="G99">
         <v>3.48</v>
@@ -9658,37 +9658,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M99">
-        <v>8.032857119999999</v>
+        <v>8.115670080000001</v>
       </c>
       <c r="N99">
-        <v>-4.618412675555556</v>
+        <v>-4.701225635555558</v>
       </c>
       <c r="O99">
-        <v>-1.385523802666667</v>
+        <v>-1.410367690666667</v>
       </c>
       <c r="P99">
-        <v>-3.232888872888889</v>
+        <v>-3.290857944888891</v>
       </c>
       <c r="Q99">
-        <v>-1.102888872888889</v>
+        <v>-1.16085794488889</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.625703875559354</v>
+        <v>3.91565581333903</v>
       </c>
       <c r="T99">
-        <v>17.98823156936251</v>
+        <v>26.98234735404376</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1275179326647022</v>
+        <v>0.1262167292701643</v>
       </c>
       <c r="W99">
-        <v>0.2057312714776632</v>
+        <v>0.2060380952380952</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4250597755490071</v>
+        <v>0.4207224309005477</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9704,22 +9704,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.280230449600114</v>
+        <v>0.282130449600114</v>
       </c>
       <c r="C100">
-        <v>-18.34197685016209</v>
+        <v>-18.79444050038231</v>
       </c>
       <c r="D100">
-        <v>12.59562314983791</v>
+        <v>12.49435949961769</v>
       </c>
       <c r="E100">
-        <v>25.6976</v>
+        <v>26.0488</v>
       </c>
       <c r="F100">
-        <v>34.4176</v>
+        <v>34.7688</v>
       </c>
       <c r="G100">
         <v>3.48</v>
@@ -9740,37 +9740,37 @@
         <v>3.414444444444444</v>
       </c>
       <c r="M100">
-        <v>8.115670080000001</v>
+        <v>8.198483039999999</v>
       </c>
       <c r="N100">
-        <v>-4.701225635555558</v>
+        <v>-4.784038595555556</v>
       </c>
       <c r="O100">
-        <v>-1.410367690666667</v>
+        <v>-1.435211578666667</v>
       </c>
       <c r="P100">
-        <v>-3.290857944888891</v>
+        <v>-3.348827016888889</v>
       </c>
       <c r="Q100">
-        <v>-1.16085794488889</v>
+        <v>-1.218827016888889</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.91565581333903</v>
+        <v>7.78551162667806</v>
       </c>
       <c r="T100">
-        <v>26.98234735404376</v>
+        <v>53.96469470808751</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1262167292701643</v>
+        <v>0.12494181281289</v>
       </c>
       <c r="W100">
-        <v>0.2060380952380952</v>
+        <v>0.2063387205387205</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9778,91 +9778,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4207224309005477</v>
+        <v>0.4164727093762999</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.282130449600114</v>
-      </c>
-      <c r="C101">
-        <v>-18.79444050038231</v>
-      </c>
-      <c r="D101">
-        <v>12.49435949961769</v>
-      </c>
-      <c r="E101">
-        <v>26.0488</v>
-      </c>
-      <c r="F101">
-        <v>34.7688</v>
-      </c>
-      <c r="G101">
-        <v>3.48</v>
-      </c>
-      <c r="H101">
-        <v>26.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.544444444444444</v>
-      </c>
-      <c r="K101">
-        <v>2.13</v>
-      </c>
-      <c r="L101">
-        <v>3.414444444444444</v>
-      </c>
-      <c r="M101">
-        <v>8.198483039999999</v>
-      </c>
-      <c r="N101">
-        <v>-4.784038595555556</v>
-      </c>
-      <c r="O101">
-        <v>-1.435211578666667</v>
-      </c>
-      <c r="P101">
-        <v>-3.348827016888889</v>
-      </c>
-      <c r="Q101">
-        <v>-1.218827016888889</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.78551162667806</v>
-      </c>
-      <c r="T101">
-        <v>53.96469470808751</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.12494181281289</v>
-      </c>
-      <c r="W101">
-        <v>0.2063387205387205</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4164727093762999</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
